--- a/samples/generated/piu_location_sweep.xlsx
+++ b/samples/generated/piu_location_sweep.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K344"/>
+  <dimension ref="A1:K347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="J111" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K111" s="7" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K118" s="9" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr">
@@ -5729,7 +5729,7 @@
       <c r="A121" s="7" t="n"/>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Rear Warning 2</t>
+          <t>Rear Warning 1</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>UPPER REAR WINDOW</t>
+          <t>LICENSE PLATE BRACKET</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>ON TAILGATE/LIFTGATE</t>
+          <t>UPPER REAR WINDOW</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>ABOVE LICENSE PLATE</t>
+          <t>ON TAILGATE/LIFTGATE</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K123" s="7" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>ON SPECIFIC BRACKET</t>
+          <t>ABOVE LICENSE PLATE</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K124" s="9" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>PILLARS</t>
+          <t>ON SPECIFIC BRACKET</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>LOWER LIFTGATE LIP</t>
+          <t>PILLARS</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>UNDER TAILGATE</t>
+          <t>LOWER LIFTGATE LIP</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>TAIL LIGHTS</t>
+          <t>UNDER TAILGATE</t>
         </is>
       </c>
       <c r="H128" s="9" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K128" s="9" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>REAR BUMPER</t>
+          <t>TAIL LIGHTS</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>REAR BUMPER</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K130" s="9" t="inlineStr">
@@ -6259,7 +6259,7 @@
       <c r="A131" s="7" t="n"/>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Rear Warning 3</t>
+          <t>Rear Warning 2</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>UPPER REAR WINDOW</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="J131" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K131" s="7" t="inlineStr">
@@ -6312,7 +6312,7 @@
       <c r="A132" s="9" t="n"/>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Rear Warning 3</t>
+          <t>Rear Warning 2</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>ON TAILGATE/LIFTGATE</t>
+          <t>LICENSE PLATE BRACKET</t>
         </is>
       </c>
       <c r="H132" s="9" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K132" s="9" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>ABOVE LICENSE PLATE</t>
+          <t>UPPER REAR WINDOW</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K133" s="7" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>ON SPECIFIC BRACKET</t>
+          <t>ON TAILGATE/LIFTGATE</t>
         </is>
       </c>
       <c r="H134" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K134" s="9" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>PILLARS</t>
+          <t>ABOVE LICENSE PLATE</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K135" s="7" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>LOWER LIFTGATE LIP</t>
+          <t>ON SPECIFIC BRACKET</t>
         </is>
       </c>
       <c r="H136" s="9" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K136" s="9" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>UNDER TAILGATE</t>
+          <t>PILLARS</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K137" s="7" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>TAIL LIGHTS</t>
+          <t>LOWER LIFTGATE LIP</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K138" s="9" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>REAR BUMPER</t>
+          <t>UNDER TAILGATE</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="J139" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K139" s="7" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>TAIL LIGHTS</t>
         </is>
       </c>
       <c r="H140" s="9" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K140" s="9" t="inlineStr">
@@ -6789,7 +6789,7 @@
       <c r="A141" s="7" t="n"/>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Rear Scene</t>
+          <t>Rear Warning 3</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -6809,15 +6809,19 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>AM-900</t>
+          <t>ION</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>ON BACK RACK</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="inlineStr"/>
+          <t>REAR BUMPER</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -6825,7 +6829,7 @@
       </c>
       <c r="J141" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K141" s="7" t="inlineStr">
@@ -6838,7 +6842,7 @@
       <c r="A142" s="9" t="n"/>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>Rear Scene</t>
+          <t>Rear Warning 3</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
@@ -6858,15 +6862,19 @@
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>AM-900</t>
+          <t>ION</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>UNDER TAILGATE</t>
-        </is>
-      </c>
-      <c r="H142" s="9" t="inlineStr"/>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
           <t>2</t>
@@ -6874,7 +6882,7 @@
       </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K142" s="9" t="inlineStr">
@@ -6887,7 +6895,7 @@
       <c r="A143" s="7" t="n"/>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>Rear Scene</t>
+          <t>Rear Warning 3</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -6907,15 +6915,19 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>AM-900</t>
+          <t>ION</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr"/>
+          <t>LICENSE PLATE BRACKET</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -6923,7 +6935,7 @@
       </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K143" s="7" t="inlineStr">
@@ -6936,7 +6948,7 @@
       <c r="A144" s="9" t="n"/>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>Lower Lift Gate Warning</t>
+          <t>Rear Scene</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
@@ -6956,19 +6968,15 @@
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>ION</t>
+          <t>AM-900</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>UPPER REAR WINDOW</t>
-        </is>
-      </c>
-      <c r="H144" s="9" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>ON BACK RACK</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr"/>
       <c r="I144" s="9" t="inlineStr">
         <is>
           <t>2</t>
@@ -6976,7 +6984,7 @@
       </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K144" s="9" t="inlineStr">
@@ -6989,7 +6997,7 @@
       <c r="A145" s="7" t="n"/>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Lower Lift Gate Warning</t>
+          <t>Rear Scene</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -7009,19 +7017,15 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>ION</t>
+          <t>AM-900</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>ON TAILGATE/LIFTGATE</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>UNDER TAILGATE</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr"/>
       <c r="I145" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -7029,7 +7033,7 @@
       </c>
       <c r="J145" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K145" s="7" t="inlineStr">
@@ -7042,7 +7046,7 @@
       <c r="A146" s="9" t="n"/>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Lower Lift Gate Warning</t>
+          <t>Rear Scene</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
@@ -7062,19 +7066,15 @@
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>ION</t>
+          <t>AM-900</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>ABOVE LICENSE PLATE</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr"/>
       <c r="I146" s="9" t="inlineStr">
         <is>
           <t>2</t>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K146" s="9" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>ON SPECIFIC BRACKET</t>
+          <t>UPPER REAR WINDOW</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="J147" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K147" s="7" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>PILLARS</t>
+          <t>ON TAILGATE/LIFTGATE</t>
         </is>
       </c>
       <c r="H148" s="9" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K148" s="9" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>LOWER LIFTGATE LIP</t>
+          <t>ABOVE LICENSE PLATE</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="J149" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K149" s="7" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>UNDER TAILGATE</t>
+          <t>ON SPECIFIC BRACKET</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K150" s="9" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>TAIL LIGHTS</t>
+          <t>PILLARS</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="J151" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K151" s="7" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>REAR BUMPER</t>
+          <t>LOWER LIFTGATE LIP</t>
         </is>
       </c>
       <c r="H152" s="9" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K152" s="9" t="inlineStr">
@@ -7438,171 +7438,201 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
+          <t>UNDER TAILGATE</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="I153" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="9" t="n"/>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>Lower Lift Gate Warning</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>ION</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>TAIL LIGHTS</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K154" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="7" t="n"/>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>Lower Lift Gate Warning</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>ION</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>REAR BUMPER</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="9" t="n"/>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>Lower Lift Gate Warning</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>ION</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
           <t>SPECIFY LOCATION</t>
         </is>
       </c>
-      <c r="H153" s="7" t="inlineStr">
+      <c r="H156" s="9" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="I153" s="7" t="inlineStr">
+      <c r="I156" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J153" s="7" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K153" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="6" t="inlineStr">
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K156" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>RADAR &amp; THERMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="9" t="n"/>
-      <c r="B155" s="10" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>STALKER</t>
-        </is>
-      </c>
-      <c r="F155" s="9" t="inlineStr">
-        <is>
-          <t>DSR</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>ON DASH</t>
-        </is>
-      </c>
-      <c r="H155" s="9" t="inlineStr"/>
-      <c r="I155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="9" t="inlineStr"/>
-      <c r="K155" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="7" t="n"/>
-      <c r="B156" s="8" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="C156" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D156" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>STALKER</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>DSR</t>
-        </is>
-      </c>
-      <c r="G156" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H156" s="7" t="inlineStr"/>
-      <c r="I156" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J156" s="7" t="inlineStr"/>
-      <c r="K156" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="9" t="n"/>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>Front Radar Antenna Mount</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D157" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E157" s="9" t="inlineStr">
-        <is>
-          <t>STALKER</t>
-        </is>
-      </c>
-      <c r="F157" s="9" t="inlineStr">
-        <is>
-          <t>LOW A BRACKET</t>
-        </is>
-      </c>
-      <c r="G157" s="9" t="inlineStr">
-        <is>
-          <t>DRIVER SIDE DASH</t>
-        </is>
-      </c>
-      <c r="H157" s="9" t="inlineStr"/>
-      <c r="I157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="9" t="inlineStr"/>
-      <c r="K157" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="7" t="n"/>
-      <c r="B158" s="12" t="inlineStr">
-        <is>
-          <t>Front Radar Antenna Mount</t>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
@@ -7622,12 +7652,12 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>LOW A BRACKET</t>
+          <t>DSR</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>ON DASH</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr"/>
@@ -7643,9 +7673,9 @@
     </row>
     <row r="159" ht="15" customHeight="1">
       <c r="A159" s="9" t="n"/>
-      <c r="B159" s="11" t="inlineStr">
-        <is>
-          <t>Rear Radar Antenna Mount</t>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -7665,12 +7695,12 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>LOW A BRACKET</t>
+          <t>DSR</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>DRIVER SIDE PILLAR</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H159" s="9" t="inlineStr"/>
@@ -7688,7 +7718,7 @@
       <c r="A160" s="7" t="n"/>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>Rear Radar Antenna Mount</t>
+          <t>Front Radar Antenna Mount</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
@@ -7713,7 +7743,7 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>DRIVER SIDE DASH</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr"/>
@@ -7729,9 +7759,9 @@
     </row>
     <row r="161" ht="15" customHeight="1">
       <c r="A161" s="9" t="n"/>
-      <c r="B161" s="10" t="inlineStr">
-        <is>
-          <t>Thermal Imager</t>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>Front Radar Antenna Mount</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -7746,17 +7776,17 @@
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>NIGHT RIDE</t>
+          <t>STALKER</t>
         </is>
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY MODEL</t>
+          <t>LOW A BRACKET</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>SPOT LIGHT MOUNT</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H161" s="9" t="inlineStr"/>
@@ -7772,9 +7802,9 @@
     </row>
     <row r="162" ht="15" customHeight="1">
       <c r="A162" s="7" t="n"/>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>Thermal Imager</t>
+      <c r="B162" s="12" t="inlineStr">
+        <is>
+          <t>Rear Radar Antenna Mount</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
@@ -7789,17 +7819,17 @@
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>NIGHT RIDE</t>
+          <t>STALKER</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY MODEL</t>
+          <t>LOW A BRACKET</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>DRIVER FENDER MOUNT</t>
+          <t>DRIVER SIDE PILLAR</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr"/>
@@ -7815,9 +7845,9 @@
     </row>
     <row r="163" ht="15" customHeight="1">
       <c r="A163" s="9" t="n"/>
-      <c r="B163" s="10" t="inlineStr">
-        <is>
-          <t>Thermal Imager</t>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>Rear Radar Antenna Mount</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
@@ -7832,17 +7862,17 @@
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
-          <t>NIGHT RIDE</t>
+          <t>STALKER</t>
         </is>
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY MODEL</t>
+          <t>LOW A BRACKET</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>PASS FENDER MOUNT</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H163" s="9" t="inlineStr"/>
@@ -7885,7 +7915,7 @@
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>LIGHT BAR MOUNT</t>
+          <t>SPOT LIGHT MOUNT</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr"/>
@@ -7928,7 +7958,7 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>DRIVER FENDER MOUNT</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr"/>
@@ -7944,9 +7974,9 @@
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" s="7" t="n"/>
-      <c r="B166" s="12" t="inlineStr">
-        <is>
-          <t>Thermal Imager Monitor</t>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Thermal Imager</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
@@ -7959,15 +7989,19 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E166" s="7" t="inlineStr"/>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>NIGHT RIDE</t>
+        </is>
+      </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>DIRECT TO COMPUTER</t>
+          <t>SPECIFY MODEL</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>ON DASH</t>
+          <t>PASS FENDER MOUNT</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr"/>
@@ -7983,9 +8017,9 @@
     </row>
     <row r="167" ht="15" customHeight="1">
       <c r="A167" s="9" t="n"/>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>Thermal Imager Monitor</t>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Thermal Imager</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -7998,15 +8032,19 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E167" s="9" t="inlineStr"/>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>NIGHT RIDE</t>
+        </is>
+      </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>DIRECT TO COMPUTER</t>
+          <t>SPECIFY MODEL</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>LIGHT BAR MOUNT</t>
         </is>
       </c>
       <c r="H167" s="9" t="inlineStr"/>
@@ -8020,139 +8058,131 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="7" t="n"/>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Thermal Imager</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>NIGHT RIDE</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY MODEL</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr"/>
+      <c r="I168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="7" t="inlineStr"/>
+      <c r="K168" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="15" customHeight="1">
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>Thermal Imager Monitor</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="inlineStr"/>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>DIRECT TO COMPUTER</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>ON DASH</t>
+        </is>
+      </c>
+      <c r="H169" s="9" t="inlineStr"/>
+      <c r="I169" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="9" t="inlineStr"/>
+      <c r="K169" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="15" customHeight="1">
+      <c r="A170" s="7" t="n"/>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>Thermal Imager Monitor</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr"/>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT TO COMPUTER</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr"/>
+      <c r="I170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="7" t="inlineStr"/>
+      <c r="K170" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>LIGHT CONTROLLER &amp; ELECTRONICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="7" t="n"/>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>Light Controller</t>
-        </is>
-      </c>
-      <c r="C169" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>ON EQUIPMENT TRAY</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr"/>
-      <c r="I169" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="7" t="inlineStr"/>
-      <c r="K169" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="9" t="n"/>
-      <c r="B170" s="10" t="inlineStr">
-        <is>
-          <t>Light Controller</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D170" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E170" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="G170" s="9" t="inlineStr">
-        <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H170" s="9" t="inlineStr"/>
-      <c r="I170" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J170" s="9" t="inlineStr"/>
-      <c r="K170" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="7" t="n"/>
-      <c r="B171" s="8" t="inlineStr">
-        <is>
-          <t>Control Head</t>
-        </is>
-      </c>
-      <c r="C171" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>CCTL5</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>IN CENTER CONSOLE</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr"/>
-      <c r="I171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J171" s="7" t="inlineStr"/>
-      <c r="K171" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8190,7 @@
       <c r="A172" s="9" t="n"/>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Control Head</t>
+          <t>Light Controller</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -8180,12 +8210,12 @@
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>CCTL5</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>RIGHT SIDE OF CONSOLE</t>
+          <t>ON EQUIPMENT TRAY</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr"/>
@@ -8203,7 +8233,7 @@
       <c r="A173" s="7" t="n"/>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>Control Head</t>
+          <t>Light Controller</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -8223,7 +8253,7 @@
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>CCTL5</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
@@ -8246,7 +8276,7 @@
       <c r="A174" s="9" t="n"/>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Expansion Module</t>
+          <t>Control Head</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -8266,12 +8296,12 @@
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>CEM8</t>
+          <t>CCTL5</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>ON EQUIPMENT TRAY</t>
+          <t>IN CENTER CONSOLE</t>
         </is>
       </c>
       <c r="H174" s="9" t="inlineStr"/>
@@ -8289,7 +8319,7 @@
       <c r="A175" s="7" t="n"/>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>Expansion Module</t>
+          <t>Control Head</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -8309,12 +8339,12 @@
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>CEM8</t>
+          <t>CCTL5</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>RIGHT SIDE OF CONSOLE</t>
         </is>
       </c>
       <c r="H175" s="7" t="inlineStr"/>
@@ -8328,271 +8358,271 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="6" t="inlineStr">
+    <row r="176" ht="15" customHeight="1">
+      <c r="A176" s="9" t="n"/>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>Control Head</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>CCTL5</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H176" s="9" t="inlineStr"/>
+      <c r="I176" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="9" t="inlineStr"/>
+      <c r="K176" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="15" customHeight="1">
+      <c r="A177" s="7" t="n"/>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>Expansion Module</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>CEM8</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>ON EQUIPMENT TRAY</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr"/>
+      <c r="I177" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="7" t="inlineStr"/>
+      <c r="K177" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="15" customHeight="1">
+      <c r="A178" s="9" t="n"/>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>Expansion Module</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>CEM8</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr"/>
+      <c r="I178" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="9" t="inlineStr"/>
+      <c r="K178" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>PA / SIREN CONTROL</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="9" t="n"/>
-      <c r="B177" s="10" t="inlineStr">
+    <row r="180" ht="15" customHeight="1">
+      <c r="A180" s="7" t="n"/>
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>Pa Mic</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E177" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F177" s="9" t="inlineStr"/>
-      <c r="G177" s="9" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr"/>
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>RIGHT SIDE OF CONSOLE</t>
         </is>
       </c>
-      <c r="H177" s="9" t="inlineStr"/>
-      <c r="I177" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J177" s="9" t="inlineStr"/>
-      <c r="K177" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="7" t="n"/>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="H180" s="7" t="inlineStr"/>
+      <c r="I180" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" s="7" t="inlineStr"/>
+      <c r="K180" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" s="9" t="n"/>
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>Pa Mic</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="7" t="inlineStr">
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr"/>
+      <c r="G181" s="9" t="inlineStr">
         <is>
           <t>DRIVERS DOOR</t>
         </is>
       </c>
-      <c r="H178" s="7" t="inlineStr"/>
-      <c r="I178" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J178" s="7" t="inlineStr"/>
-      <c r="K178" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="9" t="n"/>
-      <c r="B179" s="10" t="inlineStr">
+      <c r="H181" s="9" t="inlineStr"/>
+      <c r="I181" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="9" t="inlineStr"/>
+      <c r="K181" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="15" customHeight="1">
+      <c r="A182" s="7" t="n"/>
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>Pa Mic</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D179" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E179" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F179" s="9" t="inlineStr"/>
-      <c r="G179" s="9" t="inlineStr">
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr"/>
+      <c r="G182" s="7" t="inlineStr">
         <is>
           <t>SPECIFY LOCATION</t>
         </is>
       </c>
-      <c r="H179" s="9" t="inlineStr"/>
-      <c r="I179" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J179" s="9" t="inlineStr"/>
-      <c r="K179" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="6" t="inlineStr">
+      <c r="H182" s="7" t="inlineStr"/>
+      <c r="I182" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="7" t="inlineStr"/>
+      <c r="K182" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="16" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>RADIO &amp; COMMUNICATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="7" t="n"/>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>Radio 1</t>
-        </is>
-      </c>
-      <c r="C181" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D181" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>MOTOROLA</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>ALL IN ONE UNIT</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>FRONT OF PARTITION</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr"/>
-      <c r="I181" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J181" s="7" t="inlineStr"/>
-      <c r="K181" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="9" t="n"/>
-      <c r="B182" s="10" t="inlineStr">
-        <is>
-          <t>Radio 1</t>
-        </is>
-      </c>
-      <c r="C182" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D182" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E182" s="9" t="inlineStr">
-        <is>
-          <t>MOTOROLA</t>
-        </is>
-      </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>ALL IN ONE UNIT</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr">
-        <is>
-          <t>ON EQUIPMENT TRAY</t>
-        </is>
-      </c>
-      <c r="H182" s="9" t="inlineStr"/>
-      <c r="I182" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J182" s="9" t="inlineStr"/>
-      <c r="K182" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="7" t="n"/>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>Radio 1</t>
-        </is>
-      </c>
-      <c r="C183" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D183" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E183" s="7" t="inlineStr">
-        <is>
-          <t>MOTOROLA</t>
-        </is>
-      </c>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>ALL IN ONE UNIT</t>
-        </is>
-      </c>
-      <c r="G183" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H183" s="7" t="inlineStr"/>
-      <c r="I183" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J183" s="7" t="inlineStr"/>
-      <c r="K183" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1">
       <c r="A184" s="9" t="n"/>
-      <c r="B184" s="11" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 1</t>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>Radio 1</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
@@ -8607,13 +8637,17 @@
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>MFG CLIP</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr"/>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>ALL IN ONE UNIT</t>
+        </is>
+      </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>ON DASH</t>
+          <t>FRONT OF PARTITION</t>
         </is>
       </c>
       <c r="H184" s="9" t="inlineStr"/>
@@ -8629,9 +8663,9 @@
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="7" t="n"/>
-      <c r="B185" s="12" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 1</t>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>Radio 1</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
@@ -8646,13 +8680,17 @@
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>MFG CLIP</t>
-        </is>
-      </c>
-      <c r="F185" s="7" t="inlineStr"/>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>ALL IN ONE UNIT</t>
+        </is>
+      </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>RIGHT SIDE OF CONSOLE</t>
+          <t>ON EQUIPMENT TRAY</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr"/>
@@ -8668,9 +8706,9 @@
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="9" t="n"/>
-      <c r="B186" s="11" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 1</t>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>Radio 1</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
@@ -8685,13 +8723,17 @@
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>MFG CLIP</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr"/>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>ALL IN ONE UNIT</t>
+        </is>
+      </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>LEFT SIDE OF CONSOLE</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H186" s="9" t="inlineStr"/>
@@ -8730,7 +8772,7 @@
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>TOP PLATE OF CONSOLE</t>
+          <t>ON DASH</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr"/>
@@ -8769,7 +8811,7 @@
       <c r="F188" s="9" t="inlineStr"/>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>RIGHT SIDE OF CONSOLE</t>
         </is>
       </c>
       <c r="H188" s="9" t="inlineStr"/>
@@ -8787,7 +8829,7 @@
       <c r="A189" s="7" t="n"/>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>Radio Antenna Cable</t>
+          <t>Radio Mic Clip 1</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -8800,11 +8842,15 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E189" s="7" t="inlineStr"/>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>MFG CLIP</t>
+        </is>
+      </c>
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>REAR LEFT ROOF</t>
+          <t>LEFT SIDE OF CONSOLE</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr"/>
@@ -8822,7 +8868,7 @@
       <c r="A190" s="9" t="n"/>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>Radio Antenna Cable</t>
+          <t>Radio Mic Clip 1</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
@@ -8835,11 +8881,15 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E190" s="9" t="inlineStr"/>
+      <c r="E190" s="9" t="inlineStr">
+        <is>
+          <t>MFG CLIP</t>
+        </is>
+      </c>
       <c r="F190" s="9" t="inlineStr"/>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>LEFT CARGO WINDOW</t>
+          <t>TOP PLATE OF CONSOLE</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr"/>
@@ -8857,7 +8907,7 @@
       <c r="A191" s="7" t="n"/>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>Radio Antenna Cable</t>
+          <t>Radio Mic Clip 1</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
@@ -8870,11 +8920,15 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E191" s="7" t="inlineStr"/>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>MFG CLIP</t>
+        </is>
+      </c>
       <c r="F191" s="7" t="inlineStr"/>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>RIGHT CARGO WINDOW</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr"/>
@@ -8909,7 +8963,7 @@
       <c r="F192" s="9" t="inlineStr"/>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>REAR LEFT ROOF</t>
         </is>
       </c>
       <c r="H192" s="9" t="inlineStr"/>
@@ -8927,7 +8981,7 @@
       <c r="A193" s="7" t="n"/>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>Radio Antenna Top</t>
+          <t>Radio Antenna Cable</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -8940,19 +8994,11 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E193" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY MFG</t>
-        </is>
-      </c>
-      <c r="F193" s="7" t="inlineStr">
-        <is>
-          <t>WHIP STYLE</t>
-        </is>
-      </c>
+      <c r="E193" s="7" t="inlineStr"/>
+      <c r="F193" s="7" t="inlineStr"/>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>ON DASH</t>
+          <t>LEFT CARGO WINDOW</t>
         </is>
       </c>
       <c r="H193" s="7" t="inlineStr"/>
@@ -8970,7 +9016,7 @@
       <c r="A194" s="9" t="n"/>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>Radio Antenna Top</t>
+          <t>Radio Antenna Cable</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
@@ -8983,19 +9029,11 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E194" s="9" t="inlineStr">
-        <is>
-          <t>SPECIFY MFG</t>
-        </is>
-      </c>
-      <c r="F194" s="9" t="inlineStr">
-        <is>
-          <t>WHIP STYLE</t>
-        </is>
-      </c>
+      <c r="E194" s="9" t="inlineStr"/>
+      <c r="F194" s="9" t="inlineStr"/>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>RIGHT SIDE OF CONSOLE</t>
+          <t>RIGHT CARGO WINDOW</t>
         </is>
       </c>
       <c r="H194" s="9" t="inlineStr"/>
@@ -9013,7 +9051,7 @@
       <c r="A195" s="7" t="n"/>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>Radio Antenna Top</t>
+          <t>Radio Antenna Cable</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
@@ -9026,19 +9064,11 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E195" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY MFG</t>
-        </is>
-      </c>
-      <c r="F195" s="7" t="inlineStr">
-        <is>
-          <t>WHIP STYLE</t>
-        </is>
-      </c>
+      <c r="E195" s="7" t="inlineStr"/>
+      <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>LEFT SIDE OF CONSOLE</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr"/>
@@ -9081,7 +9111,7 @@
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>TOP PLATE OF CONSOLE</t>
+          <t>ON DASH</t>
         </is>
       </c>
       <c r="H196" s="9" t="inlineStr"/>
@@ -9124,7 +9154,7 @@
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>RIGHT SIDE OF CONSOLE</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr"/>
@@ -9140,9 +9170,9 @@
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="A198" s="9" t="n"/>
-      <c r="B198" s="10" t="inlineStr">
-        <is>
-          <t>Radio 2</t>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>Radio Antenna Top</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
@@ -9157,17 +9187,17 @@
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>MOTOROLA</t>
+          <t>SPECIFY MFG</t>
         </is>
       </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>ALL IN ONE UNIT</t>
+          <t>WHIP STYLE</t>
         </is>
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>FRONT OF PARTITION</t>
+          <t>LEFT SIDE OF CONSOLE</t>
         </is>
       </c>
       <c r="H198" s="9" t="inlineStr"/>
@@ -9183,9 +9213,9 @@
     </row>
     <row r="199" ht="15" customHeight="1">
       <c r="A199" s="7" t="n"/>
-      <c r="B199" s="8" t="inlineStr">
-        <is>
-          <t>Radio 2</t>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>Radio Antenna Top</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
@@ -9200,17 +9230,17 @@
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>MOTOROLA</t>
+          <t>SPECIFY MFG</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>ALL IN ONE UNIT</t>
+          <t>WHIP STYLE</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>ON EQUIPMENT TRAY</t>
+          <t>TOP PLATE OF CONSOLE</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr"/>
@@ -9226,9 +9256,9 @@
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="A200" s="9" t="n"/>
-      <c r="B200" s="10" t="inlineStr">
-        <is>
-          <t>Radio 2</t>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>Radio Antenna Top</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
@@ -9243,12 +9273,12 @@
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>MOTOROLA</t>
+          <t>SPECIFY MFG</t>
         </is>
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>ALL IN ONE UNIT</t>
+          <t>WHIP STYLE</t>
         </is>
       </c>
       <c r="G200" s="9" t="inlineStr">
@@ -9269,9 +9299,9 @@
     </row>
     <row r="201" ht="15" customHeight="1">
       <c r="A201" s="7" t="n"/>
-      <c r="B201" s="12" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 2</t>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>Radio 2</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
@@ -9286,13 +9316,17 @@
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>MFG CLIP</t>
-        </is>
-      </c>
-      <c r="F201" s="7" t="inlineStr"/>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>ALL IN ONE UNIT</t>
+        </is>
+      </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>ON DASH</t>
+          <t>FRONT OF PARTITION</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr"/>
@@ -9308,9 +9342,9 @@
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="A202" s="9" t="n"/>
-      <c r="B202" s="11" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 2</t>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
+          <t>Radio 2</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
@@ -9325,13 +9359,17 @@
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>MFG CLIP</t>
-        </is>
-      </c>
-      <c r="F202" s="9" t="inlineStr"/>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>ALL IN ONE UNIT</t>
+        </is>
+      </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>RIGHT SIDE OF CONSOLE</t>
+          <t>ON EQUIPMENT TRAY</t>
         </is>
       </c>
       <c r="H202" s="9" t="inlineStr"/>
@@ -9347,9 +9385,9 @@
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="7" t="n"/>
-      <c r="B203" s="12" t="inlineStr">
-        <is>
-          <t>Radio Mic Clip 2</t>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>Radio 2</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
@@ -9364,13 +9402,17 @@
       </c>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>MFG CLIP</t>
-        </is>
-      </c>
-      <c r="F203" s="7" t="inlineStr"/>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>ALL IN ONE UNIT</t>
+        </is>
+      </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>LEFT SIDE OF CONSOLE</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr"/>
@@ -9409,7 +9451,7 @@
       <c r="F204" s="9" t="inlineStr"/>
       <c r="G204" s="9" t="inlineStr">
         <is>
-          <t>TOP PLATE OF CONSOLE</t>
+          <t>ON DASH</t>
         </is>
       </c>
       <c r="H204" s="9" t="inlineStr"/>
@@ -9448,7 +9490,7 @@
       <c r="F205" s="7" t="inlineStr"/>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>RIGHT SIDE OF CONSOLE</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr"/>
@@ -9462,275 +9504,263 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="6" t="inlineStr">
+    <row r="206" ht="15" customHeight="1">
+      <c r="A206" s="9" t="n"/>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>Radio Mic Clip 2</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E206" s="9" t="inlineStr">
+        <is>
+          <t>MFG CLIP</t>
+        </is>
+      </c>
+      <c r="F206" s="9" t="inlineStr"/>
+      <c r="G206" s="9" t="inlineStr">
+        <is>
+          <t>LEFT SIDE OF CONSOLE</t>
+        </is>
+      </c>
+      <c r="H206" s="9" t="inlineStr"/>
+      <c r="I206" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J206" s="9" t="inlineStr"/>
+      <c r="K206" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="15" customHeight="1">
+      <c r="A207" s="7" t="n"/>
+      <c r="B207" s="12" t="inlineStr">
+        <is>
+          <t>Radio Mic Clip 2</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>MFG CLIP</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr"/>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>TOP PLATE OF CONSOLE</t>
+        </is>
+      </c>
+      <c r="H207" s="7" t="inlineStr"/>
+      <c r="I207" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" s="7" t="inlineStr"/>
+      <c r="K207" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" s="9" t="n"/>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>Radio Mic Clip 2</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E208" s="9" t="inlineStr">
+        <is>
+          <t>MFG CLIP</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="inlineStr"/>
+      <c r="G208" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H208" s="9" t="inlineStr"/>
+      <c r="I208" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" s="9" t="inlineStr"/>
+      <c r="K208" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="16" customHeight="1">
+      <c r="A209" s="6" t="inlineStr">
         <is>
           <t>CENTER CONSOLE &amp; COMPUTER</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="15" customHeight="1">
-      <c r="A207" s="9" t="n"/>
-      <c r="B207" s="10" t="inlineStr">
+    <row r="210" ht="15" customHeight="1">
+      <c r="A210" s="7" t="n"/>
+      <c r="B210" s="8" t="inlineStr">
         <is>
           <t>Motion Attachment</t>
         </is>
       </c>
-      <c r="C207" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D207" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E207" s="9" t="inlineStr">
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
         <is>
           <t>GAMBER JOHNSON</t>
         </is>
       </c>
-      <c r="F207" s="9" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>9"" MONGOOSE</t>
         </is>
       </c>
-      <c r="G207" s="9" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>MOUNTED TO CONSOLE</t>
         </is>
       </c>
-      <c r="H207" s="9" t="inlineStr"/>
-      <c r="I207" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J207" s="9" t="inlineStr"/>
-      <c r="K207" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="7" t="n"/>
-      <c r="B208" s="8" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr"/>
+      <c r="I210" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" s="7" t="inlineStr"/>
+      <c r="K210" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" s="9" t="n"/>
+      <c r="B211" s="10" t="inlineStr">
         <is>
           <t>Motion Attachment</t>
         </is>
       </c>
-      <c r="C208" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D208" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="inlineStr">
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
         <is>
           <t>GAMBER JOHNSON</t>
         </is>
       </c>
-      <c r="F208" s="7" t="inlineStr">
+      <c r="F211" s="9" t="inlineStr">
         <is>
           <t>9"" MONGOOSE</t>
         </is>
       </c>
-      <c r="G208" s="7" t="inlineStr">
+      <c r="G211" s="9" t="inlineStr">
         <is>
           <t>MOUNTED TO PEDESTAL</t>
         </is>
       </c>
-      <c r="H208" s="7" t="inlineStr"/>
-      <c r="I208" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J208" s="7" t="inlineStr"/>
-      <c r="K208" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="15" customHeight="1">
-      <c r="A209" s="9" t="n"/>
-      <c r="B209" s="10" t="inlineStr">
+      <c r="H211" s="9" t="inlineStr"/>
+      <c r="I211" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" s="9" t="inlineStr"/>
+      <c r="K211" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="15" customHeight="1">
+      <c r="A212" s="7" t="n"/>
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>Motion Attachment</t>
         </is>
       </c>
-      <c r="C209" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E209" s="9" t="inlineStr">
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
         <is>
           <t>GAMBER JOHNSON</t>
         </is>
       </c>
-      <c r="F209" s="9" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>9"" MONGOOSE</t>
         </is>
       </c>
-      <c r="G209" s="9" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>SPECIFY LOACTION</t>
         </is>
       </c>
-      <c r="H209" s="9" t="inlineStr"/>
-      <c r="I209" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J209" s="9" t="inlineStr"/>
-      <c r="K209" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="6" t="inlineStr">
+      <c r="H212" s="7" t="inlineStr"/>
+      <c r="I212" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" s="7" t="inlineStr"/>
+      <c r="K212" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>PRINTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="15" customHeight="1">
-      <c r="A211" s="7" t="n"/>
-      <c r="B211" s="8" t="inlineStr">
-        <is>
-          <t>Printer</t>
-        </is>
-      </c>
-      <c r="C211" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D211" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E211" s="7" t="inlineStr">
-        <is>
-          <t>BROTHER</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>PJ-822</t>
-        </is>
-      </c>
-      <c r="G211" s="7" t="inlineStr">
-        <is>
-          <t>PRINTER ARMREST MOUNT</t>
-        </is>
-      </c>
-      <c r="H211" s="7" t="inlineStr"/>
-      <c r="I211" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J211" s="7" t="inlineStr"/>
-      <c r="K211" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="9" t="n"/>
-      <c r="B212" s="10" t="inlineStr">
-        <is>
-          <t>Printer</t>
-        </is>
-      </c>
-      <c r="C212" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D212" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E212" s="9" t="inlineStr">
-        <is>
-          <t>BROTHER</t>
-        </is>
-      </c>
-      <c r="F212" s="9" t="inlineStr">
-        <is>
-          <t>PJ-822</t>
-        </is>
-      </c>
-      <c r="G212" s="9" t="inlineStr">
-        <is>
-          <t>IN CONSOLE</t>
-        </is>
-      </c>
-      <c r="H212" s="9" t="inlineStr"/>
-      <c r="I212" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J212" s="9" t="inlineStr"/>
-      <c r="K212" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="15" customHeight="1">
-      <c r="A213" s="7" t="n"/>
-      <c r="B213" s="8" t="inlineStr">
-        <is>
-          <t>Printer</t>
-        </is>
-      </c>
-      <c r="C213" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D213" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="inlineStr">
-        <is>
-          <t>BROTHER</t>
-        </is>
-      </c>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>PJ-822</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr">
-        <is>
-          <t>HEADREST MOUNT</t>
-        </is>
-      </c>
-      <c r="H213" s="7" t="inlineStr"/>
-      <c r="I213" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J213" s="7" t="inlineStr"/>
-      <c r="K213" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9793,7 @@
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>PRINTER ARMREST MOUNT</t>
         </is>
       </c>
       <c r="H214" s="9" t="inlineStr"/>
@@ -9781,7 +9811,7 @@
       <c r="A215" s="7" t="n"/>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>12v Aux Ports</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -9796,24 +9826,22 @@
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>SHO-ME</t>
+          <t>BROTHER</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>USB TYPE A</t>
+          <t>PJ-822</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>RIGHT SIDE ON CONSOLE</t>
+          <t>IN CONSOLE</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr"/>
-      <c r="I215" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I215" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="J215" s="7" t="inlineStr"/>
       <c r="K215" s="7" t="inlineStr">
@@ -9826,7 +9854,7 @@
       <c r="A216" s="9" t="n"/>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>12v Aux Ports</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="C216" s="9" t="inlineStr">
@@ -9841,24 +9869,22 @@
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>SHO-ME</t>
+          <t>BROTHER</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
         <is>
-          <t>USB TYPE A</t>
+          <t>PJ-822</t>
         </is>
       </c>
       <c r="G216" s="9" t="inlineStr">
         <is>
-          <t>IN FACEPLATE</t>
+          <t>HEADREST MOUNT</t>
         </is>
       </c>
       <c r="H216" s="9" t="inlineStr"/>
-      <c r="I216" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I216" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="J216" s="9" t="inlineStr"/>
       <c r="K216" s="9" t="inlineStr">
@@ -9871,7 +9897,7 @@
       <c r="A217" s="7" t="n"/>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>12v Aux Ports</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -9886,24 +9912,22 @@
       </c>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>SHO-ME</t>
+          <t>BROTHER</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>USB TYPE A</t>
+          <t>PJ-822</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>BACK OF CONSOLE</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr"/>
-      <c r="I217" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I217" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="J217" s="7" t="inlineStr"/>
       <c r="K217" s="7" t="inlineStr">
@@ -9941,7 +9965,7 @@
       </c>
       <c r="G218" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>RIGHT SIDE ON CONSOLE</t>
         </is>
       </c>
       <c r="H218" s="9" t="inlineStr"/>
@@ -9957,139 +9981,145 @@
         </is>
       </c>
     </row>
-    <row r="219" ht="16" customHeight="1">
-      <c r="A219" s="6" t="inlineStr">
+    <row r="219" ht="15" customHeight="1">
+      <c r="A219" s="7" t="n"/>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>12v Aux Ports</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>SHO-ME</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>USB TYPE A</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>IN FACEPLATE</t>
+        </is>
+      </c>
+      <c r="H219" s="7" t="inlineStr"/>
+      <c r="I219" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J219" s="7" t="inlineStr"/>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="15" customHeight="1">
+      <c r="A220" s="9" t="n"/>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>12v Aux Ports</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
+          <t>SHO-ME</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>USB TYPE A</t>
+        </is>
+      </c>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>BACK OF CONSOLE</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="inlineStr"/>
+      <c r="I220" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" s="9" t="inlineStr"/>
+      <c r="K220" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="15" customHeight="1">
+      <c r="A221" s="7" t="n"/>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>12v Aux Ports</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>SHO-ME</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>USB TYPE A</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr"/>
+      <c r="I221" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" s="7" t="inlineStr"/>
+      <c r="K221" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="6" t="inlineStr">
         <is>
           <t>CAMERAS &amp; DVR</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="15" customHeight="1">
-      <c r="A220" s="7" t="n"/>
-      <c r="B220" s="8" t="inlineStr">
-        <is>
-          <t>Camera DVR</t>
-        </is>
-      </c>
-      <c r="C220" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D220" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t>AXON</t>
-        </is>
-      </c>
-      <c r="F220" s="7" t="inlineStr">
-        <is>
-          <t>FLEET 3</t>
-        </is>
-      </c>
-      <c r="G220" s="7" t="inlineStr">
-        <is>
-          <t>ON FRONT PARTITION</t>
-        </is>
-      </c>
-      <c r="H220" s="7" t="inlineStr"/>
-      <c r="I220" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J220" s="7" t="inlineStr"/>
-      <c r="K220" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="9" t="n"/>
-      <c r="B221" s="10" t="inlineStr">
-        <is>
-          <t>Camera DVR</t>
-        </is>
-      </c>
-      <c r="C221" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D221" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>AXON</t>
-        </is>
-      </c>
-      <c r="F221" s="9" t="inlineStr">
-        <is>
-          <t>FLEET 3</t>
-        </is>
-      </c>
-      <c r="G221" s="9" t="inlineStr">
-        <is>
-          <t>ON EQUIPMENT TRAY</t>
-        </is>
-      </c>
-      <c r="H221" s="9" t="inlineStr"/>
-      <c r="I221" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J221" s="9" t="inlineStr"/>
-      <c r="K221" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="15" customHeight="1">
-      <c r="A222" s="7" t="n"/>
-      <c r="B222" s="8" t="inlineStr">
-        <is>
-          <t>Camera DVR</t>
-        </is>
-      </c>
-      <c r="C222" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D222" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E222" s="7" t="inlineStr">
-        <is>
-          <t>AXON</t>
-        </is>
-      </c>
-      <c r="F222" s="7" t="inlineStr">
-        <is>
-          <t>FLEET 3</t>
-        </is>
-      </c>
-      <c r="G222" s="7" t="inlineStr">
-        <is>
-          <t>IN CENTER CONSOILE</t>
-        </is>
-      </c>
-      <c r="H222" s="7" t="inlineStr"/>
-      <c r="I222" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J222" s="7" t="inlineStr"/>
-      <c r="K222" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10152,7 @@
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>ON FRONT PARTITION</t>
         </is>
       </c>
       <c r="H223" s="9" t="inlineStr"/>
@@ -10138,9 +10168,9 @@
     </row>
     <row r="224" ht="15" customHeight="1">
       <c r="A224" s="7" t="n"/>
-      <c r="B224" s="12" t="inlineStr">
-        <is>
-          <t>Body Camera Dock</t>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>Camera DVR</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
@@ -10153,11 +10183,19 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E224" s="7" t="inlineStr"/>
-      <c r="F224" s="7" t="inlineStr"/>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>FLEET 3</t>
+        </is>
+      </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>PASSENGER SIDE VISOR</t>
+          <t>ON EQUIPMENT TRAY</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr"/>
@@ -10173,9 +10211,9 @@
     </row>
     <row r="225" ht="15" customHeight="1">
       <c r="A225" s="9" t="n"/>
-      <c r="B225" s="11" t="inlineStr">
-        <is>
-          <t>Body Camera Dock</t>
+      <c r="B225" s="10" t="inlineStr">
+        <is>
+          <t>Camera DVR</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
@@ -10188,11 +10226,19 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E225" s="9" t="inlineStr"/>
-      <c r="F225" s="9" t="inlineStr"/>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>FLEET 3</t>
+        </is>
+      </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>ON CENTER CONSOLE</t>
+          <t>IN CENTER CONSOILE</t>
         </is>
       </c>
       <c r="H225" s="9" t="inlineStr"/>
@@ -10208,9 +10254,9 @@
     </row>
     <row r="226" ht="15" customHeight="1">
       <c r="A226" s="7" t="n"/>
-      <c r="B226" s="12" t="inlineStr">
-        <is>
-          <t>Body Camera Dock</t>
+      <c r="B226" s="8" t="inlineStr">
+        <is>
+          <t>Camera DVR</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -10223,11 +10269,19 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E226" s="7" t="inlineStr"/>
-      <c r="F226" s="7" t="inlineStr"/>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>FLEET 3</t>
+        </is>
+      </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
-          <t>IN GUNLOCK POCKET</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H226" s="7" t="inlineStr"/>
@@ -10262,7 +10316,7 @@
       <c r="F227" s="9" t="inlineStr"/>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>PASSENGER SIDE VISOR</t>
         </is>
       </c>
       <c r="H227" s="9" t="inlineStr"/>
@@ -10280,7 +10334,7 @@
       <c r="A228" s="7" t="n"/>
       <c r="B228" s="12" t="inlineStr">
         <is>
-          <t>Rear Seat Camera</t>
+          <t>Body Camera Dock</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
@@ -10297,7 +10351,7 @@
       <c r="F228" s="7" t="inlineStr"/>
       <c r="G228" s="7" t="inlineStr">
         <is>
-          <t>ON DRIVER SIDE HEADLINER</t>
+          <t>ON CENTER CONSOLE</t>
         </is>
       </c>
       <c r="H228" s="7" t="inlineStr"/>
@@ -10315,7 +10369,7 @@
       <c r="A229" s="9" t="n"/>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>Rear Seat Camera</t>
+          <t>Body Camera Dock</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
@@ -10332,7 +10386,7 @@
       <c r="F229" s="9" t="inlineStr"/>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>CENTER OF PARTITION</t>
+          <t>IN GUNLOCK POCKET</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr"/>
@@ -10350,7 +10404,7 @@
       <c r="A230" s="7" t="n"/>
       <c r="B230" s="12" t="inlineStr">
         <is>
-          <t>Rear Seat Camera</t>
+          <t>Body Camera Dock</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -10383,9 +10437,9 @@
     </row>
     <row r="231" ht="15" customHeight="1">
       <c r="A231" s="9" t="n"/>
-      <c r="B231" s="10" t="inlineStr">
-        <is>
-          <t>Wireless Mic Charger</t>
+      <c r="B231" s="11" t="inlineStr">
+        <is>
+          <t>Rear Seat Camera</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
@@ -10402,7 +10456,7 @@
       <c r="F231" s="9" t="inlineStr"/>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>PASSENGER SIDE VISOR</t>
+          <t>ON DRIVER SIDE HEADLINER</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr"/>
@@ -10418,9 +10472,9 @@
     </row>
     <row r="232" ht="15" customHeight="1">
       <c r="A232" s="7" t="n"/>
-      <c r="B232" s="8" t="inlineStr">
-        <is>
-          <t>Wireless Mic Charger</t>
+      <c r="B232" s="12" t="inlineStr">
+        <is>
+          <t>Rear Seat Camera</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
@@ -10437,7 +10491,7 @@
       <c r="F232" s="7" t="inlineStr"/>
       <c r="G232" s="7" t="inlineStr">
         <is>
-          <t>ON CENTER CONSOLE</t>
+          <t>CENTER OF PARTITION</t>
         </is>
       </c>
       <c r="H232" s="7" t="inlineStr"/>
@@ -10453,9 +10507,9 @@
     </row>
     <row r="233" ht="15" customHeight="1">
       <c r="A233" s="9" t="n"/>
-      <c r="B233" s="10" t="inlineStr">
-        <is>
-          <t>Wireless Mic Charger</t>
+      <c r="B233" s="11" t="inlineStr">
+        <is>
+          <t>Rear Seat Camera</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
@@ -10472,7 +10526,7 @@
       <c r="F233" s="9" t="inlineStr"/>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>IN GUNLOCK POCKET</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr"/>
@@ -10507,7 +10561,7 @@
       <c r="F234" s="7" t="inlineStr"/>
       <c r="G234" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>PASSENGER SIDE VISOR</t>
         </is>
       </c>
       <c r="H234" s="7" t="inlineStr"/>
@@ -10521,169 +10575,115 @@
         </is>
       </c>
     </row>
-    <row r="235" ht="16" customHeight="1">
-      <c r="A235" s="6" t="inlineStr">
+    <row r="235" ht="15" customHeight="1">
+      <c r="A235" s="9" t="n"/>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>Wireless Mic Charger</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr"/>
+      <c r="F235" s="9" t="inlineStr"/>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>ON CENTER CONSOLE</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr"/>
+      <c r="I235" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J235" s="9" t="inlineStr"/>
+      <c r="K235" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="15" customHeight="1">
+      <c r="A236" s="7" t="n"/>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>Wireless Mic Charger</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr"/>
+      <c r="F236" s="7" t="inlineStr"/>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>IN GUNLOCK POCKET</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr"/>
+      <c r="I236" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J236" s="7" t="inlineStr"/>
+      <c r="K236" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="15" customHeight="1">
+      <c r="A237" s="9" t="n"/>
+      <c r="B237" s="10" t="inlineStr">
+        <is>
+          <t>Wireless Mic Charger</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr"/>
+      <c r="F237" s="9" t="inlineStr"/>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr"/>
+      <c r="I237" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" s="9" t="inlineStr"/>
+      <c r="K237" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="16" customHeight="1">
+      <c r="A238" s="6" t="inlineStr">
         <is>
           <t>PARTITIONS &amp; PRISONER AREA</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="15" customHeight="1">
-      <c r="A236" s="9" t="n"/>
-      <c r="B236" s="10" t="inlineStr">
-        <is>
-          <t>Rear Seat Lights 1</t>
-        </is>
-      </c>
-      <c r="C236" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D236" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E236" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F236" s="9" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G236" s="9" t="inlineStr">
-        <is>
-          <t>LOWER KICK PANEL(S)</t>
-        </is>
-      </c>
-      <c r="H236" s="9" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I236" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J236" s="9" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K236" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="7" t="n"/>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>Rear Seat Lights 1</t>
-        </is>
-      </c>
-      <c r="C237" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D237" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E237" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F237" s="7" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G237" s="7" t="inlineStr">
-        <is>
-          <t>HEADLINER</t>
-        </is>
-      </c>
-      <c r="H237" s="7" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I237" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J237" s="7" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K237" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="15" customHeight="1">
-      <c r="A238" s="9" t="n"/>
-      <c r="B238" s="10" t="inlineStr">
-        <is>
-          <t>Rear Seat Lights 1</t>
-        </is>
-      </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E238" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr">
-        <is>
-          <t>ON FRONT PARTITION</t>
-        </is>
-      </c>
-      <c r="H238" s="9" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I238" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J238" s="9" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K238" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>LOWER KICK PANEL(S)</t>
         </is>
       </c>
       <c r="H239" s="7" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="J239" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K239" s="7" t="inlineStr">
@@ -10744,7 +10744,7 @@
       <c r="A240" s="9" t="n"/>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>Rear Seat Lights 2</t>
+          <t>Rear Seat Lights 1</t>
         </is>
       </c>
       <c r="C240" s="9" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>LOWER KICK PANEL(S)</t>
+          <t>HEADLINER</t>
         </is>
       </c>
       <c r="H240" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K240" s="9" t="inlineStr">
@@ -10797,7 +10797,7 @@
       <c r="A241" s="7" t="n"/>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Rear Seat Lights 2</t>
+          <t>Rear Seat Lights 1</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>HEADLINER</t>
+          <t>ON FRONT PARTITION</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="J241" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K241" s="7" t="inlineStr">
@@ -10850,7 +10850,7 @@
       <c r="A242" s="9" t="n"/>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>Rear Seat Lights 2</t>
+          <t>Rear Seat Lights 1</t>
         </is>
       </c>
       <c r="C242" s="9" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>ON FRONT PARTITION</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H242" s="9" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="J242" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K242" s="9" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>LOWER KICK PANEL(S)</t>
         </is>
       </c>
       <c r="H243" s="7" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="J243" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K243" s="7" t="inlineStr">
@@ -10956,7 +10956,7 @@
       <c r="A244" s="9" t="n"/>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>Rear Seat Cargo Lights</t>
+          <t>Rear Seat Lights 2</t>
         </is>
       </c>
       <c r="C244" s="9" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="J244" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K244" s="9" t="inlineStr">
@@ -11009,7 +11009,7 @@
       <c r="A245" s="7" t="n"/>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>Rear Seat Cargo Lights</t>
+          <t>Rear Seat Lights 2</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>UNDER SHELF</t>
+          <t>ON FRONT PARTITION</t>
         </is>
       </c>
       <c r="H245" s="7" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="J245" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K245" s="7" t="inlineStr">
@@ -11062,7 +11062,7 @@
       <c r="A246" s="9" t="n"/>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>Rear Seat Cargo Lights</t>
+          <t>Rear Seat Lights 2</t>
         </is>
       </c>
       <c r="C246" s="9" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G246" s="9" t="inlineStr">
         <is>
-          <t>HEADLINER AND UNDER SHELF</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H246" s="9" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="J246" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K246" s="9" t="inlineStr">
@@ -11140,163 +11140,193 @@
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
+          <t>HEADLINER</t>
+        </is>
+      </c>
+      <c r="H247" s="7" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I247" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J247" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K247" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="15" customHeight="1">
+      <c r="A248" s="9" t="n"/>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
+          <t>Rear Seat Cargo Lights</t>
+        </is>
+      </c>
+      <c r="C248" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>UNDER SHELF</t>
+        </is>
+      </c>
+      <c r="H248" s="9" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I248" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J248" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K248" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="15" customHeight="1">
+      <c r="A249" s="7" t="n"/>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>Rear Seat Cargo Lights</t>
+        </is>
+      </c>
+      <c r="C249" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="inlineStr">
+        <is>
+          <t>HEADLINER AND UNDER SHELF</t>
+        </is>
+      </c>
+      <c r="H249" s="7" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I249" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J249" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K249" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="15" customHeight="1">
+      <c r="A250" s="9" t="n"/>
+      <c r="B250" s="10" t="inlineStr">
+        <is>
+          <t>Rear Seat Cargo Lights</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
           <t>SPECIFY LOCATION(S)</t>
         </is>
       </c>
-      <c r="H247" s="7" t="inlineStr">
+      <c r="H250" s="9" t="inlineStr">
         <is>
           <t>RED</t>
         </is>
       </c>
-      <c r="I247" s="7" t="inlineStr">
+      <c r="I250" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J247" s="7" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K247" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="16" customHeight="1">
-      <c r="A248" s="6" t="inlineStr">
+      <c r="J250" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
+      <c r="K250" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="16" customHeight="1">
+      <c r="A251" s="6" t="inlineStr">
         <is>
           <t>ARMOR &amp; PROTECTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="15" customHeight="1">
-      <c r="A249" s="9" t="n"/>
-      <c r="B249" s="10" t="inlineStr">
-        <is>
-          <t>Bullet Proof Door Panel(s)</t>
-        </is>
-      </c>
-      <c r="C249" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D249" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E249" s="9" t="inlineStr">
-        <is>
-          <t>ANGEL ARMOR</t>
-        </is>
-      </c>
-      <c r="F249" s="9" t="inlineStr">
-        <is>
-          <t>LEVEL 3A (HANDGUN)</t>
-        </is>
-      </c>
-      <c r="G249" s="9" t="inlineStr">
-        <is>
-          <t>DRIVERS DOOR ONLY</t>
-        </is>
-      </c>
-      <c r="H249" s="9" t="inlineStr"/>
-      <c r="I249" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J249" s="9" t="inlineStr"/>
-      <c r="K249" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="15" customHeight="1">
-      <c r="A250" s="7" t="n"/>
-      <c r="B250" s="8" t="inlineStr">
-        <is>
-          <t>Bullet Proof Door Panel(s)</t>
-        </is>
-      </c>
-      <c r="C250" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D250" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E250" s="7" t="inlineStr">
-        <is>
-          <t>ANGEL ARMOR</t>
-        </is>
-      </c>
-      <c r="F250" s="7" t="inlineStr">
-        <is>
-          <t>LEVEL 3A (HANDGUN)</t>
-        </is>
-      </c>
-      <c r="G250" s="7" t="inlineStr">
-        <is>
-          <t>DRIVER AND PASSENGER FRONT DOORS</t>
-        </is>
-      </c>
-      <c r="H250" s="7" t="inlineStr"/>
-      <c r="I250" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J250" s="7" t="inlineStr"/>
-      <c r="K250" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="15" customHeight="1">
-      <c r="A251" s="9" t="n"/>
-      <c r="B251" s="10" t="inlineStr">
-        <is>
-          <t>Bullet Proof Door Panel(s)</t>
-        </is>
-      </c>
-      <c r="C251" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D251" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E251" s="9" t="inlineStr">
-        <is>
-          <t>ANGEL ARMOR</t>
-        </is>
-      </c>
-      <c r="F251" s="9" t="inlineStr">
-        <is>
-          <t>LEVEL 3A (HANDGUN)</t>
-        </is>
-      </c>
-      <c r="G251" s="9" t="inlineStr">
-        <is>
-          <t>SPECIFY DOOR(S)</t>
-        </is>
-      </c>
-      <c r="H251" s="9" t="inlineStr"/>
-      <c r="I251" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J251" s="9" t="inlineStr"/>
-      <c r="K251" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11334,7 @@
       <c r="A252" s="7" t="n"/>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>Bullet Proof Door Window(s)</t>
+          <t>Bullet Proof Door Panel(s)</t>
         </is>
       </c>
       <c r="C252" s="7" t="inlineStr">
@@ -11319,7 +11349,7 @@
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY MFG</t>
+          <t>ANGEL ARMOR</t>
         </is>
       </c>
       <c r="F252" s="7" t="inlineStr">
@@ -11347,7 +11377,7 @@
       <c r="A253" s="9" t="n"/>
       <c r="B253" s="10" t="inlineStr">
         <is>
-          <t>Bullet Proof Door Window(s)</t>
+          <t>Bullet Proof Door Panel(s)</t>
         </is>
       </c>
       <c r="C253" s="9" t="inlineStr">
@@ -11362,7 +11392,7 @@
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY MFG</t>
+          <t>ANGEL ARMOR</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
@@ -11390,7 +11420,7 @@
       <c r="A254" s="7" t="n"/>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>Bullet Proof Door Window(s)</t>
+          <t>Bullet Proof Door Panel(s)</t>
         </is>
       </c>
       <c r="C254" s="7" t="inlineStr">
@@ -11405,7 +11435,7 @@
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY MFG</t>
+          <t>ANGEL ARMOR</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
@@ -11415,7 +11445,7 @@
       </c>
       <c r="G254" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY WINDOW(S)</t>
+          <t>SPECIFY DOOR(S)</t>
         </is>
       </c>
       <c r="H254" s="7" t="inlineStr"/>
@@ -11429,169 +11459,139 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="16" customHeight="1">
-      <c r="A255" s="6" t="inlineStr">
+    <row r="255" ht="15" customHeight="1">
+      <c r="A255" s="9" t="n"/>
+      <c r="B255" s="10" t="inlineStr">
+        <is>
+          <t>Bullet Proof Door Window(s)</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY MFG</t>
+        </is>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>LEVEL 3A (HANDGUN)</t>
+        </is>
+      </c>
+      <c r="G255" s="9" t="inlineStr">
+        <is>
+          <t>DRIVERS DOOR ONLY</t>
+        </is>
+      </c>
+      <c r="H255" s="9" t="inlineStr"/>
+      <c r="I255" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" s="9" t="inlineStr"/>
+      <c r="K255" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="15" customHeight="1">
+      <c r="A256" s="7" t="n"/>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
+          <t>Bullet Proof Door Window(s)</t>
+        </is>
+      </c>
+      <c r="C256" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY MFG</t>
+        </is>
+      </c>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>LEVEL 3A (HANDGUN)</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>DRIVER AND PASSENGER FRONT DOORS</t>
+        </is>
+      </c>
+      <c r="H256" s="7" t="inlineStr"/>
+      <c r="I256" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" s="7" t="inlineStr"/>
+      <c r="K256" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="15" customHeight="1">
+      <c r="A257" s="9" t="n"/>
+      <c r="B257" s="10" t="inlineStr">
+        <is>
+          <t>Bullet Proof Door Window(s)</t>
+        </is>
+      </c>
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY MFG</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>LEVEL 3A (HANDGUN)</t>
+        </is>
+      </c>
+      <c r="G257" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY WINDOW(S)</t>
+        </is>
+      </c>
+      <c r="H257" s="9" t="inlineStr"/>
+      <c r="I257" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J257" s="9" t="inlineStr"/>
+      <c r="K257" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="16" customHeight="1">
+      <c r="A258" s="6" t="inlineStr">
         <is>
           <t>CARGO &amp; STORAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="9" t="n"/>
-      <c r="B256" s="10" t="inlineStr">
-        <is>
-          <t>Cargo Lighting</t>
-        </is>
-      </c>
-      <c r="C256" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D256" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E256" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F256" s="9" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G256" s="9" t="inlineStr">
-        <is>
-          <t>ON LIFT GATE</t>
-        </is>
-      </c>
-      <c r="H256" s="9" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I256" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J256" s="9" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K256" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="15" customHeight="1">
-      <c r="A257" s="7" t="n"/>
-      <c r="B257" s="8" t="inlineStr">
-        <is>
-          <t>Cargo Lighting</t>
-        </is>
-      </c>
-      <c r="C257" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D257" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E257" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F257" s="7" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G257" s="7" t="inlineStr">
-        <is>
-          <t>HEADLINER</t>
-        </is>
-      </c>
-      <c r="H257" s="7" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I257" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J257" s="7" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K257" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="15" customHeight="1">
-      <c r="A258" s="9" t="n"/>
-      <c r="B258" s="10" t="inlineStr">
-        <is>
-          <t>Cargo Lighting</t>
-        </is>
-      </c>
-      <c r="C258" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E258" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F258" s="9" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G258" s="9" t="inlineStr">
-        <is>
-          <t>ON LIFTGATE AND HEADLINER</t>
-        </is>
-      </c>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I258" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J258" s="9" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
-      <c r="K258" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION(S)</t>
+          <t>ON LIFT GATE</t>
         </is>
       </c>
       <c r="H259" s="7" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="J259" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K259" s="7" t="inlineStr">
@@ -11652,7 +11652,7 @@
       <c r="A260" s="9" t="n"/>
       <c r="B260" s="10" t="inlineStr">
         <is>
-          <t>Door Lock Button</t>
+          <t>Cargo Lighting</t>
         </is>
       </c>
       <c r="C260" s="9" t="inlineStr">
@@ -11665,18 +11665,36 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E260" s="9" t="inlineStr"/>
-      <c r="F260" s="9" t="inlineStr"/>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
-          <t>ON LEFT D-PILLAR</t>
-        </is>
-      </c>
-      <c r="H260" s="9" t="inlineStr"/>
-      <c r="I260" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J260" s="9" t="inlineStr"/>
+          <t>HEADLINER</t>
+        </is>
+      </c>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I260" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J260" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
       <c r="K260" s="9" t="inlineStr">
         <is>
           <t>loc sweep</t>
@@ -11687,7 +11705,7 @@
       <c r="A261" s="7" t="n"/>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>Door Lock Button</t>
+          <t>Cargo Lighting</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -11700,18 +11718,36 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E261" s="7" t="inlineStr"/>
-      <c r="F261" s="7" t="inlineStr"/>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
       <c r="G261" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H261" s="7" t="inlineStr"/>
-      <c r="I261" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J261" s="7" t="inlineStr"/>
+          <t>ON LIFTGATE AND HEADLINER</t>
+        </is>
+      </c>
+      <c r="H261" s="7" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I261" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J261" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
       <c r="K261" s="7" t="inlineStr">
         <is>
           <t>loc sweep</t>
@@ -11722,7 +11758,7 @@
       <c r="A262" s="9" t="n"/>
       <c r="B262" s="10" t="inlineStr">
         <is>
-          <t>Equipment Tray</t>
+          <t>Cargo Lighting</t>
         </is>
       </c>
       <c r="C262" s="9" t="inlineStr">
@@ -11737,24 +11773,34 @@
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>SETINA</t>
+          <t>WHELEN</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>EQUIPMENT DRAWER</t>
+          <t>3"" ROUND</t>
         </is>
       </c>
       <c r="G262" s="9" t="inlineStr">
         <is>
-          <t>ON REAR PARTITION</t>
-        </is>
-      </c>
-      <c r="H262" s="9" t="inlineStr"/>
-      <c r="I262" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J262" s="9" t="inlineStr"/>
+          <t>SPECIFY LOCATION(S)</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I262" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J262" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
       <c r="K262" s="9" t="inlineStr">
         <is>
           <t>loc sweep</t>
@@ -11765,7 +11811,7 @@
       <c r="A263" s="7" t="n"/>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>Equipment Tray</t>
+          <t>Door Lock Button</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -11778,19 +11824,11 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E263" s="7" t="inlineStr">
-        <is>
-          <t>SETINA</t>
-        </is>
-      </c>
-      <c r="F263" s="7" t="inlineStr">
-        <is>
-          <t>EQUIPMENT DRAWER</t>
-        </is>
-      </c>
+      <c r="E263" s="7" t="inlineStr"/>
+      <c r="F263" s="7" t="inlineStr"/>
       <c r="G263" s="7" t="inlineStr">
         <is>
-          <t>UNDER CARGO BOX</t>
+          <t>ON LEFT D-PILLAR</t>
         </is>
       </c>
       <c r="H263" s="7" t="inlineStr"/>
@@ -11808,7 +11846,7 @@
       <c r="A264" s="9" t="n"/>
       <c r="B264" s="10" t="inlineStr">
         <is>
-          <t>Equipment Tray</t>
+          <t>Door Lock Button</t>
         </is>
       </c>
       <c r="C264" s="9" t="inlineStr">
@@ -11821,19 +11859,11 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E264" s="9" t="inlineStr">
-        <is>
-          <t>SETINA</t>
-        </is>
-      </c>
-      <c r="F264" s="9" t="inlineStr">
-        <is>
-          <t>EQUIPMENT DRAWER</t>
-        </is>
-      </c>
+      <c r="E264" s="9" t="inlineStr"/>
+      <c r="F264" s="9" t="inlineStr"/>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>PART OF CARGO MAXX</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr"/>
@@ -11876,7 +11906,7 @@
       </c>
       <c r="G265" s="7" t="inlineStr">
         <is>
-          <t>CARGO AREA FLOOR</t>
+          <t>ON REAR PARTITION</t>
         </is>
       </c>
       <c r="H265" s="7" t="inlineStr"/>
@@ -11919,7 +11949,7 @@
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>ON REAR SEAT</t>
+          <t>UNDER CARGO BOX</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr"/>
@@ -11962,7 +11992,7 @@
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>IN CONSOLE</t>
+          <t>PART OF CARGO MAXX</t>
         </is>
       </c>
       <c r="H267" s="7" t="inlineStr"/>
@@ -12005,7 +12035,7 @@
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOACTION</t>
+          <t>CARGO AREA FLOOR</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr"/>
@@ -12019,139 +12049,139 @@
         </is>
       </c>
     </row>
-    <row r="269" ht="16" customHeight="1">
-      <c r="A269" s="6" t="inlineStr">
+    <row r="269" ht="15" customHeight="1">
+      <c r="A269" s="7" t="n"/>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>Equipment Tray</t>
+        </is>
+      </c>
+      <c r="C269" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D269" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E269" s="7" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F269" s="7" t="inlineStr">
+        <is>
+          <t>EQUIPMENT DRAWER</t>
+        </is>
+      </c>
+      <c r="G269" s="7" t="inlineStr">
+        <is>
+          <t>ON REAR SEAT</t>
+        </is>
+      </c>
+      <c r="H269" s="7" t="inlineStr"/>
+      <c r="I269" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" s="7" t="inlineStr"/>
+      <c r="K269" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="15" customHeight="1">
+      <c r="A270" s="9" t="n"/>
+      <c r="B270" s="10" t="inlineStr">
+        <is>
+          <t>Equipment Tray</t>
+        </is>
+      </c>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E270" s="9" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>EQUIPMENT DRAWER</t>
+        </is>
+      </c>
+      <c r="G270" s="9" t="inlineStr">
+        <is>
+          <t>IN CONSOLE</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="inlineStr"/>
+      <c r="I270" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J270" s="9" t="inlineStr"/>
+      <c r="K270" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="15" customHeight="1">
+      <c r="A271" s="7" t="n"/>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>Equipment Tray</t>
+        </is>
+      </c>
+      <c r="C271" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D271" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E271" s="7" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>EQUIPMENT DRAWER</t>
+        </is>
+      </c>
+      <c r="G271" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOACTION</t>
+        </is>
+      </c>
+      <c r="H271" s="7" t="inlineStr"/>
+      <c r="I271" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" s="7" t="inlineStr"/>
+      <c r="K271" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="16" customHeight="1">
+      <c r="A272" s="6" t="inlineStr">
         <is>
           <t>GUNLOCKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="15" customHeight="1">
-      <c r="A270" s="7" t="n"/>
-      <c r="B270" s="8" t="inlineStr">
-        <is>
-          <t>Gunlock 1</t>
-        </is>
-      </c>
-      <c r="C270" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D270" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E270" s="7" t="inlineStr">
-        <is>
-          <t>SANTA CRUZ</t>
-        </is>
-      </c>
-      <c r="F270" s="7" t="inlineStr">
-        <is>
-          <t>SINGLE HANDCUFF</t>
-        </is>
-      </c>
-      <c r="G270" s="7" t="inlineStr">
-        <is>
-          <t>OVERHEAD ON FRONT PARTITION</t>
-        </is>
-      </c>
-      <c r="H270" s="7" t="inlineStr"/>
-      <c r="I270" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J270" s="7" t="inlineStr"/>
-      <c r="K270" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="15" customHeight="1">
-      <c r="A271" s="9" t="n"/>
-      <c r="B271" s="10" t="inlineStr">
-        <is>
-          <t>Gunlock 1</t>
-        </is>
-      </c>
-      <c r="C271" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D271" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E271" s="9" t="inlineStr">
-        <is>
-          <t>SANTA CRUZ</t>
-        </is>
-      </c>
-      <c r="F271" s="9" t="inlineStr">
-        <is>
-          <t>SINGLE HANDCUFF</t>
-        </is>
-      </c>
-      <c r="G271" s="9" t="inlineStr">
-        <is>
-          <t>GUN LOCK POCKET</t>
-        </is>
-      </c>
-      <c r="H271" s="9" t="inlineStr"/>
-      <c r="I271" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J271" s="9" t="inlineStr"/>
-      <c r="K271" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="15" customHeight="1">
-      <c r="A272" s="7" t="n"/>
-      <c r="B272" s="8" t="inlineStr">
-        <is>
-          <t>Gunlock 1</t>
-        </is>
-      </c>
-      <c r="C272" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D272" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E272" s="7" t="inlineStr">
-        <is>
-          <t>SANTA CRUZ</t>
-        </is>
-      </c>
-      <c r="F272" s="7" t="inlineStr">
-        <is>
-          <t>SINGLE HANDCUFF</t>
-        </is>
-      </c>
-      <c r="G272" s="7" t="inlineStr">
-        <is>
-          <t>LEFT GUN LOCK POCKET</t>
-        </is>
-      </c>
-      <c r="H272" s="7" t="inlineStr"/>
-      <c r="I272" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J272" s="7" t="inlineStr"/>
-      <c r="K272" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12214,7 @@
       </c>
       <c r="G273" s="9" t="inlineStr">
         <is>
-          <t>RIGHT GUN LOCK POCKET</t>
+          <t>OVERHEAD ON FRONT PARTITION</t>
         </is>
       </c>
       <c r="H273" s="9" t="inlineStr"/>
@@ -12227,7 +12257,7 @@
       </c>
       <c r="G274" s="7" t="inlineStr">
         <is>
-          <t>OVER HEAD IN REAR</t>
+          <t>GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H274" s="7" t="inlineStr"/>
@@ -12270,7 +12300,7 @@
       </c>
       <c r="G275" s="9" t="inlineStr">
         <is>
-          <t>CARGO AREA MOUNT (SPECIFY)</t>
+          <t>LEFT GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H275" s="9" t="inlineStr"/>
@@ -12313,7 +12343,7 @@
       </c>
       <c r="G276" s="7" t="inlineStr">
         <is>
-          <t>REAR SEAT MOUNT</t>
+          <t>RIGHT GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H276" s="7" t="inlineStr"/>
@@ -12356,7 +12386,7 @@
       </c>
       <c r="G277" s="9" t="inlineStr">
         <is>
-          <t>SINGLE PRISIONER FACING FORWARD</t>
+          <t>OVER HEAD IN REAR</t>
         </is>
       </c>
       <c r="H277" s="9" t="inlineStr"/>
@@ -12399,7 +12429,7 @@
       </c>
       <c r="G278" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>CARGO AREA MOUNT (SPECIFY)</t>
         </is>
       </c>
       <c r="H278" s="7" t="inlineStr"/>
@@ -12417,7 +12447,7 @@
       <c r="A279" s="9" t="n"/>
       <c r="B279" s="10" t="inlineStr">
         <is>
-          <t>Gunlock 2</t>
+          <t>Gunlock 1</t>
         </is>
       </c>
       <c r="C279" s="9" t="inlineStr">
@@ -12442,7 +12472,7 @@
       </c>
       <c r="G279" s="9" t="inlineStr">
         <is>
-          <t>OVERHEAD ON FRONT PARTITION</t>
+          <t>REAR SEAT MOUNT</t>
         </is>
       </c>
       <c r="H279" s="9" t="inlineStr"/>
@@ -12460,7 +12490,7 @@
       <c r="A280" s="7" t="n"/>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>Gunlock 2</t>
+          <t>Gunlock 1</t>
         </is>
       </c>
       <c r="C280" s="7" t="inlineStr">
@@ -12485,7 +12515,7 @@
       </c>
       <c r="G280" s="7" t="inlineStr">
         <is>
-          <t>GUN LOCK POCKET</t>
+          <t>SINGLE PRISIONER FACING FORWARD</t>
         </is>
       </c>
       <c r="H280" s="7" t="inlineStr"/>
@@ -12503,7 +12533,7 @@
       <c r="A281" s="9" t="n"/>
       <c r="B281" s="10" t="inlineStr">
         <is>
-          <t>Gunlock 2</t>
+          <t>Gunlock 1</t>
         </is>
       </c>
       <c r="C281" s="9" t="inlineStr">
@@ -12528,7 +12558,7 @@
       </c>
       <c r="G281" s="9" t="inlineStr">
         <is>
-          <t>LEFT GUN LOCK POCKET</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H281" s="9" t="inlineStr"/>
@@ -12571,7 +12601,7 @@
       </c>
       <c r="G282" s="7" t="inlineStr">
         <is>
-          <t>RIGHT GUN LOCK POCKET</t>
+          <t>OVERHEAD ON FRONT PARTITION</t>
         </is>
       </c>
       <c r="H282" s="7" t="inlineStr"/>
@@ -12614,7 +12644,7 @@
       </c>
       <c r="G283" s="9" t="inlineStr">
         <is>
-          <t>OVER HEAD IN REAR</t>
+          <t>GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H283" s="9" t="inlineStr"/>
@@ -12657,7 +12687,7 @@
       </c>
       <c r="G284" s="7" t="inlineStr">
         <is>
-          <t>CARGO AREA MOUNT (SPECIFY)</t>
+          <t>LEFT GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H284" s="7" t="inlineStr"/>
@@ -12700,7 +12730,7 @@
       </c>
       <c r="G285" s="9" t="inlineStr">
         <is>
-          <t>REAR SEAT MOUNT</t>
+          <t>RIGHT GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H285" s="9" t="inlineStr"/>
@@ -12743,7 +12773,7 @@
       </c>
       <c r="G286" s="7" t="inlineStr">
         <is>
-          <t>SINGLE PRISIONER FACING FORWARD</t>
+          <t>OVER HEAD IN REAR</t>
         </is>
       </c>
       <c r="H286" s="7" t="inlineStr"/>
@@ -12786,7 +12816,7 @@
       </c>
       <c r="G287" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>CARGO AREA MOUNT (SPECIFY)</t>
         </is>
       </c>
       <c r="H287" s="9" t="inlineStr"/>
@@ -12804,7 +12834,7 @@
       <c r="A288" s="7" t="n"/>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>Gunlock 3</t>
+          <t>Gunlock 2</t>
         </is>
       </c>
       <c r="C288" s="7" t="inlineStr">
@@ -12829,7 +12859,7 @@
       </c>
       <c r="G288" s="7" t="inlineStr">
         <is>
-          <t>OVERHEAD ON FRONT PARTITION</t>
+          <t>REAR SEAT MOUNT</t>
         </is>
       </c>
       <c r="H288" s="7" t="inlineStr"/>
@@ -12847,7 +12877,7 @@
       <c r="A289" s="9" t="n"/>
       <c r="B289" s="10" t="inlineStr">
         <is>
-          <t>Gunlock 3</t>
+          <t>Gunlock 2</t>
         </is>
       </c>
       <c r="C289" s="9" t="inlineStr">
@@ -12872,7 +12902,7 @@
       </c>
       <c r="G289" s="9" t="inlineStr">
         <is>
-          <t>GUN LOCK POCKET</t>
+          <t>SINGLE PRISIONER FACING FORWARD</t>
         </is>
       </c>
       <c r="H289" s="9" t="inlineStr"/>
@@ -12890,7 +12920,7 @@
       <c r="A290" s="7" t="n"/>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>Gunlock 3</t>
+          <t>Gunlock 2</t>
         </is>
       </c>
       <c r="C290" s="7" t="inlineStr">
@@ -12915,7 +12945,7 @@
       </c>
       <c r="G290" s="7" t="inlineStr">
         <is>
-          <t>LEFT GUN LOCK POCKET</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H290" s="7" t="inlineStr"/>
@@ -12958,7 +12988,7 @@
       </c>
       <c r="G291" s="9" t="inlineStr">
         <is>
-          <t>RIGHT GUN LOCK POCKET</t>
+          <t>OVERHEAD ON FRONT PARTITION</t>
         </is>
       </c>
       <c r="H291" s="9" t="inlineStr"/>
@@ -13001,7 +13031,7 @@
       </c>
       <c r="G292" s="7" t="inlineStr">
         <is>
-          <t>OVER HEAD IN REAR</t>
+          <t>GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H292" s="7" t="inlineStr"/>
@@ -13044,7 +13074,7 @@
       </c>
       <c r="G293" s="9" t="inlineStr">
         <is>
-          <t>CARGO AREA MOUNT (SPECIFY)</t>
+          <t>LEFT GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H293" s="9" t="inlineStr"/>
@@ -13087,7 +13117,7 @@
       </c>
       <c r="G294" s="7" t="inlineStr">
         <is>
-          <t>REAR SEAT MOUNT</t>
+          <t>RIGHT GUN LOCK POCKET</t>
         </is>
       </c>
       <c r="H294" s="7" t="inlineStr"/>
@@ -13130,7 +13160,7 @@
       </c>
       <c r="G295" s="9" t="inlineStr">
         <is>
-          <t>SINGLE PRISIONER FACING FORWARD</t>
+          <t>OVER HEAD IN REAR</t>
         </is>
       </c>
       <c r="H295" s="9" t="inlineStr"/>
@@ -13173,7 +13203,7 @@
       </c>
       <c r="G296" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>CARGO AREA MOUNT (SPECIFY)</t>
         </is>
       </c>
       <c r="H296" s="7" t="inlineStr"/>
@@ -13187,139 +13217,139 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="16" customHeight="1">
-      <c r="A297" s="6" t="inlineStr">
+    <row r="297" ht="15" customHeight="1">
+      <c r="A297" s="9" t="n"/>
+      <c r="B297" s="10" t="inlineStr">
+        <is>
+          <t>Gunlock 3</t>
+        </is>
+      </c>
+      <c r="C297" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E297" s="9" t="inlineStr">
+        <is>
+          <t>SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="F297" s="9" t="inlineStr">
+        <is>
+          <t>SINGLE HANDCUFF</t>
+        </is>
+      </c>
+      <c r="G297" s="9" t="inlineStr">
+        <is>
+          <t>REAR SEAT MOUNT</t>
+        </is>
+      </c>
+      <c r="H297" s="9" t="inlineStr"/>
+      <c r="I297" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J297" s="9" t="inlineStr"/>
+      <c r="K297" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="15" customHeight="1">
+      <c r="A298" s="7" t="n"/>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 3</t>
+        </is>
+      </c>
+      <c r="C298" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D298" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E298" s="7" t="inlineStr">
+        <is>
+          <t>SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="F298" s="7" t="inlineStr">
+        <is>
+          <t>SINGLE HANDCUFF</t>
+        </is>
+      </c>
+      <c r="G298" s="7" t="inlineStr">
+        <is>
+          <t>SINGLE PRISIONER FACING FORWARD</t>
+        </is>
+      </c>
+      <c r="H298" s="7" t="inlineStr"/>
+      <c r="I298" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J298" s="7" t="inlineStr"/>
+      <c r="K298" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="15" customHeight="1">
+      <c r="A299" s="9" t="n"/>
+      <c r="B299" s="10" t="inlineStr">
+        <is>
+          <t>Gunlock 3</t>
+        </is>
+      </c>
+      <c r="C299" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E299" s="9" t="inlineStr">
+        <is>
+          <t>SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="F299" s="9" t="inlineStr">
+        <is>
+          <t>SINGLE HANDCUFF</t>
+        </is>
+      </c>
+      <c r="G299" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H299" s="9" t="inlineStr"/>
+      <c r="I299" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" s="9" t="inlineStr"/>
+      <c r="K299" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="16" customHeight="1">
+      <c r="A300" s="6" t="inlineStr">
         <is>
           <t>K-9 EQUIPMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="15" customHeight="1">
-      <c r="A298" s="9" t="n"/>
-      <c r="B298" s="10" t="inlineStr">
-        <is>
-          <t>K-9 Heat Alarm/Popper</t>
-        </is>
-      </c>
-      <c r="C298" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D298" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E298" s="9" t="inlineStr">
-        <is>
-          <t>ACE K-9</t>
-        </is>
-      </c>
-      <c r="F298" s="9" t="inlineStr">
-        <is>
-          <t>HEAT ALARM ONLY</t>
-        </is>
-      </c>
-      <c r="G298" s="9" t="inlineStr">
-        <is>
-          <t>ON FRONT OF K-9 PARTITION</t>
-        </is>
-      </c>
-      <c r="H298" s="9" t="inlineStr"/>
-      <c r="I298" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J298" s="9" t="inlineStr"/>
-      <c r="K298" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="15" customHeight="1">
-      <c r="A299" s="7" t="n"/>
-      <c r="B299" s="8" t="inlineStr">
-        <is>
-          <t>K-9 Heat Alarm/Popper</t>
-        </is>
-      </c>
-      <c r="C299" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D299" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E299" s="7" t="inlineStr">
-        <is>
-          <t>ACE K-9</t>
-        </is>
-      </c>
-      <c r="F299" s="7" t="inlineStr">
-        <is>
-          <t>HEAT ALARM ONLY</t>
-        </is>
-      </c>
-      <c r="G299" s="7" t="inlineStr">
-        <is>
-          <t>ON EQUIPMEBNT TRAY</t>
-        </is>
-      </c>
-      <c r="H299" s="7" t="inlineStr"/>
-      <c r="I299" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J299" s="7" t="inlineStr"/>
-      <c r="K299" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="15" customHeight="1">
-      <c r="A300" s="9" t="n"/>
-      <c r="B300" s="10" t="inlineStr">
-        <is>
-          <t>K-9 Heat Alarm/Popper</t>
-        </is>
-      </c>
-      <c r="C300" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D300" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E300" s="9" t="inlineStr">
-        <is>
-          <t>ACE K-9</t>
-        </is>
-      </c>
-      <c r="F300" s="9" t="inlineStr">
-        <is>
-          <t>HEAT ALARM ONLY</t>
-        </is>
-      </c>
-      <c r="G300" s="9" t="inlineStr">
-        <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H300" s="9" t="inlineStr"/>
-      <c r="I300" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J300" s="9" t="inlineStr"/>
-      <c r="K300" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13357,7 @@
       <c r="A301" s="7" t="n"/>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>K-9 Control Head</t>
+          <t>K-9 Heat Alarm/Popper</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
@@ -13345,10 +13375,14 @@
           <t>ACE K-9</t>
         </is>
       </c>
-      <c r="F301" s="7" t="inlineStr"/>
+      <c r="F301" s="7" t="inlineStr">
+        <is>
+          <t>HEAT ALARM ONLY</t>
+        </is>
+      </c>
       <c r="G301" s="7" t="inlineStr">
         <is>
-          <t>IN CENTER CONSOLE</t>
+          <t>ON FRONT OF K-9 PARTITION</t>
         </is>
       </c>
       <c r="H301" s="7" t="inlineStr"/>
@@ -13366,7 +13400,7 @@
       <c r="A302" s="9" t="n"/>
       <c r="B302" s="10" t="inlineStr">
         <is>
-          <t>K-9 Control Head</t>
+          <t>K-9 Heat Alarm/Popper</t>
         </is>
       </c>
       <c r="C302" s="9" t="inlineStr">
@@ -13384,10 +13418,14 @@
           <t>ACE K-9</t>
         </is>
       </c>
-      <c r="F302" s="9" t="inlineStr"/>
+      <c r="F302" s="9" t="inlineStr">
+        <is>
+          <t>HEAT ALARM ONLY</t>
+        </is>
+      </c>
       <c r="G302" s="9" t="inlineStr">
         <is>
-          <t>PASSENGER SIDE VISOR</t>
+          <t>ON EQUIPMEBNT TRAY</t>
         </is>
       </c>
       <c r="H302" s="9" t="inlineStr"/>
@@ -13405,7 +13443,7 @@
       <c r="A303" s="7" t="n"/>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>K-9 Control Head</t>
+          <t>K-9 Heat Alarm/Popper</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
@@ -13423,10 +13461,14 @@
           <t>ACE K-9</t>
         </is>
       </c>
-      <c r="F303" s="7" t="inlineStr"/>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>HEAT ALARM ONLY</t>
+        </is>
+      </c>
       <c r="G303" s="7" t="inlineStr">
         <is>
-          <t>TOP PLATE OF CONSOLE</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H303" s="7" t="inlineStr"/>
@@ -13465,7 +13507,7 @@
       <c r="F304" s="9" t="inlineStr"/>
       <c r="G304" s="9" t="inlineStr">
         <is>
-          <t>RIGHT OF CONSOLE</t>
+          <t>IN CENTER CONSOLE</t>
         </is>
       </c>
       <c r="H304" s="9" t="inlineStr"/>
@@ -13504,7 +13546,7 @@
       <c r="F305" s="7" t="inlineStr"/>
       <c r="G305" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>PASSENGER SIDE VISOR</t>
         </is>
       </c>
       <c r="H305" s="7" t="inlineStr"/>
@@ -13522,7 +13564,7 @@
       <c r="A306" s="9" t="n"/>
       <c r="B306" s="10" t="inlineStr">
         <is>
-          <t>K-9 Add-Ons</t>
+          <t>K-9 Control Head</t>
         </is>
       </c>
       <c r="C306" s="9" t="inlineStr">
@@ -13543,7 +13585,7 @@
       <c r="F306" s="9" t="inlineStr"/>
       <c r="G306" s="9" t="inlineStr">
         <is>
-          <t>IN CENTER CONSOLE</t>
+          <t>TOP PLATE OF CONSOLE</t>
         </is>
       </c>
       <c r="H306" s="9" t="inlineStr"/>
@@ -13561,7 +13603,7 @@
       <c r="A307" s="7" t="n"/>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>K-9 Add-Ons</t>
+          <t>K-9 Control Head</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
@@ -13582,7 +13624,7 @@
       <c r="F307" s="7" t="inlineStr"/>
       <c r="G307" s="7" t="inlineStr">
         <is>
-          <t>PASSENGER SIDE VISOR</t>
+          <t>RIGHT OF CONSOLE</t>
         </is>
       </c>
       <c r="H307" s="7" t="inlineStr"/>
@@ -13600,7 +13642,7 @@
       <c r="A308" s="9" t="n"/>
       <c r="B308" s="10" t="inlineStr">
         <is>
-          <t>K-9 Add-Ons</t>
+          <t>K-9 Control Head</t>
         </is>
       </c>
       <c r="C308" s="9" t="inlineStr">
@@ -13621,7 +13663,7 @@
       <c r="F308" s="9" t="inlineStr"/>
       <c r="G308" s="9" t="inlineStr">
         <is>
-          <t>TOP PLATE OF CONSOLE</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H308" s="9" t="inlineStr"/>
@@ -13660,7 +13702,7 @@
       <c r="F309" s="7" t="inlineStr"/>
       <c r="G309" s="7" t="inlineStr">
         <is>
-          <t>RIGHT OF CONSOLE</t>
+          <t>IN CENTER CONSOLE</t>
         </is>
       </c>
       <c r="H309" s="7" t="inlineStr"/>
@@ -13699,7 +13741,7 @@
       <c r="F310" s="9" t="inlineStr"/>
       <c r="G310" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>PASSENGER SIDE VISOR</t>
         </is>
       </c>
       <c r="H310" s="9" t="inlineStr"/>
@@ -13713,127 +13755,127 @@
         </is>
       </c>
     </row>
-    <row r="311" ht="16" customHeight="1">
-      <c r="A311" s="6" t="inlineStr">
+    <row r="311" ht="15" customHeight="1">
+      <c r="A311" s="7" t="n"/>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>K-9 Add-Ons</t>
+        </is>
+      </c>
+      <c r="C311" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D311" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E311" s="7" t="inlineStr">
+        <is>
+          <t>ACE K-9</t>
+        </is>
+      </c>
+      <c r="F311" s="7" t="inlineStr"/>
+      <c r="G311" s="7" t="inlineStr">
+        <is>
+          <t>TOP PLATE OF CONSOLE</t>
+        </is>
+      </c>
+      <c r="H311" s="7" t="inlineStr"/>
+      <c r="I311" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J311" s="7" t="inlineStr"/>
+      <c r="K311" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="15" customHeight="1">
+      <c r="A312" s="9" t="n"/>
+      <c r="B312" s="10" t="inlineStr">
+        <is>
+          <t>K-9 Add-Ons</t>
+        </is>
+      </c>
+      <c r="C312" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D312" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E312" s="9" t="inlineStr">
+        <is>
+          <t>ACE K-9</t>
+        </is>
+      </c>
+      <c r="F312" s="9" t="inlineStr"/>
+      <c r="G312" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT OF CONSOLE</t>
+        </is>
+      </c>
+      <c r="H312" s="9" t="inlineStr"/>
+      <c r="I312" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J312" s="9" t="inlineStr"/>
+      <c r="K312" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="15" customHeight="1">
+      <c r="A313" s="7" t="n"/>
+      <c r="B313" s="8" t="inlineStr">
+        <is>
+          <t>K-9 Add-Ons</t>
+        </is>
+      </c>
+      <c r="C313" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D313" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E313" s="7" t="inlineStr">
+        <is>
+          <t>ACE K-9</t>
+        </is>
+      </c>
+      <c r="F313" s="7" t="inlineStr"/>
+      <c r="G313" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H313" s="7" t="inlineStr"/>
+      <c r="I313" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" s="7" t="inlineStr"/>
+      <c r="K313" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="16" customHeight="1">
+      <c r="A314" s="6" t="inlineStr">
         <is>
           <t>ELECTRICAL &amp; POWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="15" customHeight="1">
-      <c r="A312" s="7" t="n"/>
-      <c r="B312" s="8" t="inlineStr">
-        <is>
-          <t>Battery Tender</t>
-        </is>
-      </c>
-      <c r="C312" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D312" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E312" s="7" t="inlineStr">
-        <is>
-          <t>SCHUMACHER</t>
-        </is>
-      </c>
-      <c r="F312" s="7" t="inlineStr"/>
-      <c r="G312" s="7" t="inlineStr">
-        <is>
-          <t>ON EQUIPMENT TRAY</t>
-        </is>
-      </c>
-      <c r="H312" s="7" t="inlineStr"/>
-      <c r="I312" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J312" s="7" t="inlineStr"/>
-      <c r="K312" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="15" customHeight="1">
-      <c r="A313" s="9" t="n"/>
-      <c r="B313" s="10" t="inlineStr">
-        <is>
-          <t>Battery Tender</t>
-        </is>
-      </c>
-      <c r="C313" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D313" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E313" s="9" t="inlineStr">
-        <is>
-          <t>SCHUMACHER</t>
-        </is>
-      </c>
-      <c r="F313" s="9" t="inlineStr"/>
-      <c r="G313" s="9" t="inlineStr">
-        <is>
-          <t>UNDER HOOD</t>
-        </is>
-      </c>
-      <c r="H313" s="9" t="inlineStr"/>
-      <c r="I313" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J313" s="9" t="inlineStr"/>
-      <c r="K313" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="15" customHeight="1">
-      <c r="A314" s="7" t="n"/>
-      <c r="B314" s="8" t="inlineStr">
-        <is>
-          <t>Battery Tender</t>
-        </is>
-      </c>
-      <c r="C314" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D314" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E314" s="7" t="inlineStr">
-        <is>
-          <t>SCHUMACHER</t>
-        </is>
-      </c>
-      <c r="F314" s="7" t="inlineStr"/>
-      <c r="G314" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY LOCATION</t>
-        </is>
-      </c>
-      <c r="H314" s="7" t="inlineStr"/>
-      <c r="I314" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J314" s="7" t="inlineStr"/>
-      <c r="K314" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -13841,7 +13883,7 @@
       <c r="A315" s="9" t="n"/>
       <c r="B315" s="10" t="inlineStr">
         <is>
-          <t>Auto Eject</t>
+          <t>Battery Tender</t>
         </is>
       </c>
       <c r="C315" s="9" t="inlineStr">
@@ -13856,17 +13898,13 @@
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>KUSSMAUL</t>
-        </is>
-      </c>
-      <c r="F315" s="9" t="inlineStr">
-        <is>
-          <t>WATER PROOF</t>
-        </is>
-      </c>
+          <t>SCHUMACHER</t>
+        </is>
+      </c>
+      <c r="F315" s="9" t="inlineStr"/>
       <c r="G315" s="9" t="inlineStr">
         <is>
-          <t>LEFT FRONT QUARTER PANEL</t>
+          <t>ON EQUIPMENT TRAY</t>
         </is>
       </c>
       <c r="H315" s="9" t="inlineStr"/>
@@ -13884,7 +13922,7 @@
       <c r="A316" s="7" t="n"/>
       <c r="B316" s="8" t="inlineStr">
         <is>
-          <t>Auto Eject</t>
+          <t>Battery Tender</t>
         </is>
       </c>
       <c r="C316" s="7" t="inlineStr">
@@ -13899,17 +13937,13 @@
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>KUSSMAUL</t>
-        </is>
-      </c>
-      <c r="F316" s="7" t="inlineStr">
-        <is>
-          <t>WATER PROOF</t>
-        </is>
-      </c>
+          <t>SCHUMACHER</t>
+        </is>
+      </c>
+      <c r="F316" s="7" t="inlineStr"/>
       <c r="G316" s="7" t="inlineStr">
         <is>
-          <t>LEFT REAR QUARTER PANEL</t>
+          <t>UNDER HOOD</t>
         </is>
       </c>
       <c r="H316" s="7" t="inlineStr"/>
@@ -13927,7 +13961,7 @@
       <c r="A317" s="9" t="n"/>
       <c r="B317" s="10" t="inlineStr">
         <is>
-          <t>Auto Eject</t>
+          <t>Battery Tender</t>
         </is>
       </c>
       <c r="C317" s="9" t="inlineStr">
@@ -13942,17 +13976,13 @@
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>KUSSMAUL</t>
-        </is>
-      </c>
-      <c r="F317" s="9" t="inlineStr">
-        <is>
-          <t>WATER PROOF</t>
-        </is>
-      </c>
+          <t>SCHUMACHER</t>
+        </is>
+      </c>
+      <c r="F317" s="9" t="inlineStr"/>
       <c r="G317" s="9" t="inlineStr">
         <is>
-          <t>ON BACK RACK</t>
+          <t>SPECIFY LOCATION</t>
         </is>
       </c>
       <c r="H317" s="9" t="inlineStr"/>
@@ -13995,7 +14025,7 @@
       </c>
       <c r="G318" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>LEFT FRONT QUARTER PANEL</t>
         </is>
       </c>
       <c r="H318" s="7" t="inlineStr"/>
@@ -14009,131 +14039,139 @@
         </is>
       </c>
     </row>
-    <row r="319" ht="16" customHeight="1">
-      <c r="A319" s="6" t="inlineStr">
+    <row r="319" ht="15" customHeight="1">
+      <c r="A319" s="9" t="n"/>
+      <c r="B319" s="10" t="inlineStr">
+        <is>
+          <t>Auto Eject</t>
+        </is>
+      </c>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E319" s="9" t="inlineStr">
+        <is>
+          <t>KUSSMAUL</t>
+        </is>
+      </c>
+      <c r="F319" s="9" t="inlineStr">
+        <is>
+          <t>WATER PROOF</t>
+        </is>
+      </c>
+      <c r="G319" s="9" t="inlineStr">
+        <is>
+          <t>LEFT REAR QUARTER PANEL</t>
+        </is>
+      </c>
+      <c r="H319" s="9" t="inlineStr"/>
+      <c r="I319" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J319" s="9" t="inlineStr"/>
+      <c r="K319" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="15" customHeight="1">
+      <c r="A320" s="7" t="n"/>
+      <c r="B320" s="8" t="inlineStr">
+        <is>
+          <t>Auto Eject</t>
+        </is>
+      </c>
+      <c r="C320" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D320" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E320" s="7" t="inlineStr">
+        <is>
+          <t>KUSSMAUL</t>
+        </is>
+      </c>
+      <c r="F320" s="7" t="inlineStr">
+        <is>
+          <t>WATER PROOF</t>
+        </is>
+      </c>
+      <c r="G320" s="7" t="inlineStr">
+        <is>
+          <t>ON BACK RACK</t>
+        </is>
+      </c>
+      <c r="H320" s="7" t="inlineStr"/>
+      <c r="I320" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J320" s="7" t="inlineStr"/>
+      <c r="K320" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="15" customHeight="1">
+      <c r="A321" s="9" t="n"/>
+      <c r="B321" s="10" t="inlineStr">
+        <is>
+          <t>Auto Eject</t>
+        </is>
+      </c>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D321" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E321" s="9" t="inlineStr">
+        <is>
+          <t>KUSSMAUL</t>
+        </is>
+      </c>
+      <c r="F321" s="9" t="inlineStr">
+        <is>
+          <t>WATER PROOF</t>
+        </is>
+      </c>
+      <c r="G321" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H321" s="9" t="inlineStr"/>
+      <c r="I321" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J321" s="9" t="inlineStr"/>
+      <c r="K321" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="16" customHeight="1">
+      <c r="A322" s="6" t="inlineStr">
         <is>
           <t>CONNECTED SYSTEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="320" ht="15" customHeight="1">
-      <c r="A320" s="9" t="n"/>
-      <c r="B320" s="10" t="inlineStr">
-        <is>
-          <t>Vehicle to Vehicle Sync</t>
-        </is>
-      </c>
-      <c r="C320" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D320" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E320" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F320" s="9" t="inlineStr"/>
-      <c r="G320" s="9" t="inlineStr">
-        <is>
-          <t>IN LIGHT BAR</t>
-        </is>
-      </c>
-      <c r="H320" s="9" t="inlineStr"/>
-      <c r="I320" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J320" s="9" t="inlineStr"/>
-      <c r="K320" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="321" ht="15" customHeight="1">
-      <c r="A321" s="7" t="n"/>
-      <c r="B321" s="8" t="inlineStr">
-        <is>
-          <t>Vehicle to Vehicle Sync</t>
-        </is>
-      </c>
-      <c r="C321" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D321" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E321" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F321" s="7" t="inlineStr"/>
-      <c r="G321" s="7" t="inlineStr">
-        <is>
-          <t>ON CARGO WINDOW</t>
-        </is>
-      </c>
-      <c r="H321" s="7" t="inlineStr"/>
-      <c r="I321" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J321" s="7" t="inlineStr"/>
-      <c r="K321" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="322" ht="15" customHeight="1">
-      <c r="A322" s="9" t="n"/>
-      <c r="B322" s="10" t="inlineStr">
-        <is>
-          <t>Cloud System</t>
-        </is>
-      </c>
-      <c r="C322" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D322" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E322" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F322" s="9" t="inlineStr">
-        <is>
-          <t>VERIZON ROOF MOUNT</t>
-        </is>
-      </c>
-      <c r="G322" s="9" t="inlineStr">
-        <is>
-          <t>ON EQUIPMENT TRAY</t>
-        </is>
-      </c>
-      <c r="H322" s="9" t="inlineStr"/>
-      <c r="I322" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J322" s="9" t="inlineStr"/>
-      <c r="K322" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14179,7 @@
       <c r="A323" s="7" t="n"/>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Cloud System</t>
+          <t>Vehicle to Vehicle Sync</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -14159,14 +14197,10 @@
           <t>WHELEN</t>
         </is>
       </c>
-      <c r="F323" s="7" t="inlineStr">
-        <is>
-          <t>VERIZON ROOF MOUNT</t>
-        </is>
-      </c>
+      <c r="F323" s="7" t="inlineStr"/>
       <c r="G323" s="7" t="inlineStr">
         <is>
-          <t>FRONT OF PARTITION</t>
+          <t>IN LIGHT BAR</t>
         </is>
       </c>
       <c r="H323" s="7" t="inlineStr"/>
@@ -14184,7 +14218,7 @@
       <c r="A324" s="9" t="n"/>
       <c r="B324" s="10" t="inlineStr">
         <is>
-          <t>Cloud System</t>
+          <t>Vehicle to Vehicle Sync</t>
         </is>
       </c>
       <c r="C324" s="9" t="inlineStr">
@@ -14202,14 +14236,10 @@
           <t>WHELEN</t>
         </is>
       </c>
-      <c r="F324" s="9" t="inlineStr">
-        <is>
-          <t>VERIZON ROOF MOUNT</t>
-        </is>
-      </c>
+      <c r="F324" s="9" t="inlineStr"/>
       <c r="G324" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>ON CARGO WINDOW</t>
         </is>
       </c>
       <c r="H324" s="9" t="inlineStr"/>
@@ -14223,145 +14253,139 @@
         </is>
       </c>
     </row>
-    <row r="325" ht="16" customHeight="1">
-      <c r="A325" s="6" t="inlineStr">
+    <row r="325" ht="15" customHeight="1">
+      <c r="A325" s="7" t="n"/>
+      <c r="B325" s="8" t="inlineStr">
+        <is>
+          <t>Cloud System</t>
+        </is>
+      </c>
+      <c r="C325" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D325" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E325" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F325" s="7" t="inlineStr">
+        <is>
+          <t>VERIZON ROOF MOUNT</t>
+        </is>
+      </c>
+      <c r="G325" s="7" t="inlineStr">
+        <is>
+          <t>ON EQUIPMENT TRAY</t>
+        </is>
+      </c>
+      <c r="H325" s="7" t="inlineStr"/>
+      <c r="I325" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J325" s="7" t="inlineStr"/>
+      <c r="K325" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="15" customHeight="1">
+      <c r="A326" s="9" t="n"/>
+      <c r="B326" s="10" t="inlineStr">
+        <is>
+          <t>Cloud System</t>
+        </is>
+      </c>
+      <c r="C326" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D326" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E326" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F326" s="9" t="inlineStr">
+        <is>
+          <t>VERIZON ROOF MOUNT</t>
+        </is>
+      </c>
+      <c r="G326" s="9" t="inlineStr">
+        <is>
+          <t>FRONT OF PARTITION</t>
+        </is>
+      </c>
+      <c r="H326" s="9" t="inlineStr"/>
+      <c r="I326" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J326" s="9" t="inlineStr"/>
+      <c r="K326" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="15" customHeight="1">
+      <c r="A327" s="7" t="n"/>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Cloud System</t>
+        </is>
+      </c>
+      <c r="C327" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D327" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E327" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F327" s="7" t="inlineStr">
+        <is>
+          <t>VERIZON ROOF MOUNT</t>
+        </is>
+      </c>
+      <c r="G327" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H327" s="7" t="inlineStr"/>
+      <c r="I327" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J327" s="7" t="inlineStr"/>
+      <c r="K327" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="16" customHeight="1">
+      <c r="A328" s="6" t="inlineStr">
         <is>
           <t>ARGES &amp; SPOTLIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="15" customHeight="1">
-      <c r="A326" s="7" t="n"/>
-      <c r="B326" s="8" t="inlineStr">
-        <is>
-          <t>Arges</t>
-        </is>
-      </c>
-      <c r="C326" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D326" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E326" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F326" s="7" t="inlineStr">
-        <is>
-          <t>PRO-FOCUS</t>
-        </is>
-      </c>
-      <c r="G326" s="7" t="inlineStr">
-        <is>
-          <t>LEFT FRONT FENDER</t>
-        </is>
-      </c>
-      <c r="H326" s="7" t="inlineStr"/>
-      <c r="I326" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J326" s="7" t="inlineStr"/>
-      <c r="K326" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="327" ht="15" customHeight="1">
-      <c r="A327" s="9" t="n"/>
-      <c r="B327" s="10" t="inlineStr">
-        <is>
-          <t>Arges</t>
-        </is>
-      </c>
-      <c r="C327" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D327" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E327" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F327" s="9" t="inlineStr">
-        <is>
-          <t>PRO-FOCUS</t>
-        </is>
-      </c>
-      <c r="G327" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT FRONT FENDER</t>
-        </is>
-      </c>
-      <c r="H327" s="9" t="inlineStr"/>
-      <c r="I327" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J327" s="9" t="inlineStr"/>
-      <c r="K327" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="328" ht="15" customHeight="1">
-      <c r="A328" s="7" t="n"/>
-      <c r="B328" s="8" t="inlineStr">
-        <is>
-          <t>Arges</t>
-        </is>
-      </c>
-      <c r="C328" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D328" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E328" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F328" s="7" t="inlineStr">
-        <is>
-          <t>PRO-FOCUS</t>
-        </is>
-      </c>
-      <c r="G328" s="7" t="inlineStr">
-        <is>
-          <t>LEFT AND RIGHT FENDER</t>
-        </is>
-      </c>
-      <c r="H328" s="7" t="inlineStr"/>
-      <c r="I328" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J328" s="7" t="inlineStr"/>
-      <c r="K328" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -14394,7 +14418,7 @@
       </c>
       <c r="G329" s="9" t="inlineStr">
         <is>
-          <t>LIGHTBAR MOUNT</t>
+          <t>LEFT FRONT FENDER</t>
         </is>
       </c>
       <c r="H329" s="9" t="inlineStr"/>
@@ -14439,7 +14463,7 @@
       </c>
       <c r="G330" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY LOCATION</t>
+          <t>RIGHT FRONT FENDER</t>
         </is>
       </c>
       <c r="H330" s="7" t="inlineStr"/>
@@ -14457,9 +14481,9 @@
     </row>
     <row r="331" ht="15" customHeight="1">
       <c r="A331" s="9" t="n"/>
-      <c r="B331" s="11" t="inlineStr">
-        <is>
-          <t>Arges Controller</t>
+      <c r="B331" s="10" t="inlineStr">
+        <is>
+          <t>Arges</t>
         </is>
       </c>
       <c r="C331" s="9" t="inlineStr">
@@ -14479,17 +14503,19 @@
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>ARGES W/ BAIL BRACKET</t>
+          <t>PRO-FOCUS</t>
         </is>
       </c>
       <c r="G331" s="9" t="inlineStr">
         <is>
-          <t>LEFT ON DASH</t>
+          <t>LEFT AND RIGHT FENDER</t>
         </is>
       </c>
       <c r="H331" s="9" t="inlineStr"/>
-      <c r="I331" s="9" t="n">
-        <v>1</v>
+      <c r="I331" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J331" s="9" t="inlineStr"/>
       <c r="K331" s="9" t="inlineStr">
@@ -14500,9 +14526,9 @@
     </row>
     <row r="332" ht="15" customHeight="1">
       <c r="A332" s="7" t="n"/>
-      <c r="B332" s="12" t="inlineStr">
-        <is>
-          <t>Arges Controller</t>
+      <c r="B332" s="8" t="inlineStr">
+        <is>
+          <t>Arges</t>
         </is>
       </c>
       <c r="C332" s="7" t="inlineStr">
@@ -14522,17 +14548,19 @@
       </c>
       <c r="F332" s="7" t="inlineStr">
         <is>
-          <t>ARGES W/ BAIL BRACKET</t>
+          <t>PRO-FOCUS</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
         <is>
-          <t>IN CENTER CONSOLE</t>
+          <t>LIGHTBAR MOUNT</t>
         </is>
       </c>
       <c r="H332" s="7" t="inlineStr"/>
-      <c r="I332" s="7" t="n">
-        <v>1</v>
+      <c r="I332" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J332" s="7" t="inlineStr"/>
       <c r="K332" s="7" t="inlineStr">
@@ -14543,9 +14571,9 @@
     </row>
     <row r="333" ht="15" customHeight="1">
       <c r="A333" s="9" t="n"/>
-      <c r="B333" s="11" t="inlineStr">
-        <is>
-          <t>Arges Controller</t>
+      <c r="B333" s="10" t="inlineStr">
+        <is>
+          <t>Arges</t>
         </is>
       </c>
       <c r="C333" s="9" t="inlineStr">
@@ -14565,7 +14593,7 @@
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>ARGES W/ BAIL BRACKET</t>
+          <t>PRO-FOCUS</t>
         </is>
       </c>
       <c r="G333" s="9" t="inlineStr">
@@ -14574,8 +14602,10 @@
         </is>
       </c>
       <c r="H333" s="9" t="inlineStr"/>
-      <c r="I333" s="9" t="n">
-        <v>1</v>
+      <c r="I333" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J333" s="9" t="inlineStr"/>
       <c r="K333" s="9" t="inlineStr">
@@ -14584,139 +14614,139 @@
         </is>
       </c>
     </row>
-    <row r="334" ht="16" customHeight="1">
-      <c r="A334" s="6" t="inlineStr">
+    <row r="334" ht="15" customHeight="1">
+      <c r="A334" s="7" t="n"/>
+      <c r="B334" s="12" t="inlineStr">
+        <is>
+          <t>Arges Controller</t>
+        </is>
+      </c>
+      <c r="C334" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D334" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E334" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F334" s="7" t="inlineStr">
+        <is>
+          <t>ARGES W/ BAIL BRACKET</t>
+        </is>
+      </c>
+      <c r="G334" s="7" t="inlineStr">
+        <is>
+          <t>LEFT ON DASH</t>
+        </is>
+      </c>
+      <c r="H334" s="7" t="inlineStr"/>
+      <c r="I334" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J334" s="7" t="inlineStr"/>
+      <c r="K334" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="15" customHeight="1">
+      <c r="A335" s="9" t="n"/>
+      <c r="B335" s="11" t="inlineStr">
+        <is>
+          <t>Arges Controller</t>
+        </is>
+      </c>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>ARGES W/ BAIL BRACKET</t>
+        </is>
+      </c>
+      <c r="G335" s="9" t="inlineStr">
+        <is>
+          <t>IN CENTER CONSOLE</t>
+        </is>
+      </c>
+      <c r="H335" s="9" t="inlineStr"/>
+      <c r="I335" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J335" s="9" t="inlineStr"/>
+      <c r="K335" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="15" customHeight="1">
+      <c r="A336" s="7" t="n"/>
+      <c r="B336" s="12" t="inlineStr">
+        <is>
+          <t>Arges Controller</t>
+        </is>
+      </c>
+      <c r="C336" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D336" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E336" s="7" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F336" s="7" t="inlineStr">
+        <is>
+          <t>ARGES W/ BAIL BRACKET</t>
+        </is>
+      </c>
+      <c r="G336" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY LOCATION</t>
+        </is>
+      </c>
+      <c r="H336" s="7" t="inlineStr"/>
+      <c r="I336" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J336" s="7" t="inlineStr"/>
+      <c r="K336" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="16" customHeight="1">
+      <c r="A337" s="6" t="inlineStr">
         <is>
           <t>FINISHING &amp; ACCESSORIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="15" customHeight="1">
-      <c r="A335" s="7" t="n"/>
-      <c r="B335" s="8" t="inlineStr">
-        <is>
-          <t>Floor Mats</t>
-        </is>
-      </c>
-      <c r="C335" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D335" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E335" s="7" t="inlineStr">
-        <is>
-          <t>WEATHER TECH</t>
-        </is>
-      </c>
-      <c r="F335" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY MODEL</t>
-        </is>
-      </c>
-      <c r="G335" s="7" t="inlineStr">
-        <is>
-          <t>FRONT DRIVER AND PASSENGER</t>
-        </is>
-      </c>
-      <c r="H335" s="7" t="inlineStr"/>
-      <c r="I335" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J335" s="7" t="inlineStr"/>
-      <c r="K335" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="15" customHeight="1">
-      <c r="A336" s="9" t="n"/>
-      <c r="B336" s="10" t="inlineStr">
-        <is>
-          <t>Floor Mats</t>
-        </is>
-      </c>
-      <c r="C336" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D336" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E336" s="9" t="inlineStr">
-        <is>
-          <t>WEATHER TECH</t>
-        </is>
-      </c>
-      <c r="F336" s="9" t="inlineStr">
-        <is>
-          <t>SPECIFY MODEL</t>
-        </is>
-      </c>
-      <c r="G336" s="9" t="inlineStr">
-        <is>
-          <t>FRONT AND REAR</t>
-        </is>
-      </c>
-      <c r="H336" s="9" t="inlineStr"/>
-      <c r="I336" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J336" s="9" t="inlineStr"/>
-      <c r="K336" s="9" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="15" customHeight="1">
-      <c r="A337" s="7" t="n"/>
-      <c r="B337" s="8" t="inlineStr">
-        <is>
-          <t>Floor Mats</t>
-        </is>
-      </c>
-      <c r="C337" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D337" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E337" s="7" t="inlineStr">
-        <is>
-          <t>WEATHER TECH</t>
-        </is>
-      </c>
-      <c r="F337" s="7" t="inlineStr">
-        <is>
-          <t>SPECIFY MODEL</t>
-        </is>
-      </c>
-      <c r="G337" s="7" t="inlineStr">
-        <is>
-          <t>FRONT REAR AND CARGO</t>
-        </is>
-      </c>
-      <c r="H337" s="7" t="inlineStr"/>
-      <c r="I337" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J337" s="7" t="inlineStr"/>
-      <c r="K337" s="7" t="inlineStr">
-        <is>
-          <t>loc sweep</t>
         </is>
       </c>
     </row>
@@ -14749,7 +14779,7 @@
       </c>
       <c r="G338" s="9" t="inlineStr">
         <is>
-          <t>CARGO MAT</t>
+          <t>FRONT DRIVER AND PASSENGER</t>
         </is>
       </c>
       <c r="H338" s="9" t="inlineStr"/>
@@ -14767,7 +14797,7 @@
       <c r="A339" s="7" t="n"/>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Seat Covers</t>
+          <t>Floor Mats</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -14782,24 +14812,20 @@
       </c>
       <c r="E339" s="7" t="inlineStr">
         <is>
-          <t>TIGER TOUGH</t>
+          <t>WEATHER TECH</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>SPECIFY MODEL</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
         <is>
-          <t>DRIVER ONLY</t>
-        </is>
-      </c>
-      <c r="H339" s="7" t="inlineStr">
-        <is>
-          <t>BLACK</t>
-        </is>
-      </c>
+          <t>FRONT AND REAR</t>
+        </is>
+      </c>
+      <c r="H339" s="7" t="inlineStr"/>
       <c r="I339" s="7" t="n">
         <v>1</v>
       </c>
@@ -14814,7 +14840,7 @@
       <c r="A340" s="9" t="n"/>
       <c r="B340" s="10" t="inlineStr">
         <is>
-          <t>Seat Covers</t>
+          <t>Floor Mats</t>
         </is>
       </c>
       <c r="C340" s="9" t="inlineStr">
@@ -14829,24 +14855,20 @@
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>TIGER TOUGH</t>
+          <t>WEATHER TECH</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>SPECIFY MODEL</t>
         </is>
       </c>
       <c r="G340" s="9" t="inlineStr">
         <is>
-          <t>DRIVER AND PASSENGER</t>
-        </is>
-      </c>
-      <c r="H340" s="9" t="inlineStr">
-        <is>
-          <t>BLACK</t>
-        </is>
-      </c>
+          <t>FRONT REAR AND CARGO</t>
+        </is>
+      </c>
+      <c r="H340" s="9" t="inlineStr"/>
       <c r="I340" s="9" t="n">
         <v>1</v>
       </c>
@@ -14861,7 +14883,7 @@
       <c r="A341" s="7" t="n"/>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Seat Covers</t>
+          <t>Floor Mats</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -14876,24 +14898,20 @@
       </c>
       <c r="E341" s="7" t="inlineStr">
         <is>
-          <t>TIGER TOUGH</t>
+          <t>WEATHER TECH</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>SPECIFY MODEL</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
         <is>
-          <t>FULL FRONT</t>
-        </is>
-      </c>
-      <c r="H341" s="7" t="inlineStr">
-        <is>
-          <t>BLACK</t>
-        </is>
-      </c>
+          <t>CARGO MAT</t>
+        </is>
+      </c>
+      <c r="H341" s="7" t="inlineStr"/>
       <c r="I341" s="7" t="n">
         <v>1</v>
       </c>
@@ -14933,7 +14951,7 @@
       </c>
       <c r="G342" s="9" t="inlineStr">
         <is>
-          <t>FULL REAR</t>
+          <t>DRIVER ONLY</t>
         </is>
       </c>
       <c r="H342" s="9" t="inlineStr">
@@ -14980,7 +14998,7 @@
       </c>
       <c r="G343" s="7" t="inlineStr">
         <is>
-          <t>FRONT AND REAR</t>
+          <t>DRIVER AND PASSENGER</t>
         </is>
       </c>
       <c r="H343" s="7" t="inlineStr">
@@ -15027,7 +15045,7 @@
       </c>
       <c r="G344" s="9" t="inlineStr">
         <is>
-          <t>SPECIFY MODEL</t>
+          <t>FULL FRONT</t>
         </is>
       </c>
       <c r="H344" s="9" t="inlineStr">
@@ -15045,57 +15063,198 @@
         </is>
       </c>
     </row>
+    <row r="345" ht="15" customHeight="1">
+      <c r="A345" s="7" t="n"/>
+      <c r="B345" s="8" t="inlineStr">
+        <is>
+          <t>Seat Covers</t>
+        </is>
+      </c>
+      <c r="C345" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D345" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E345" s="7" t="inlineStr">
+        <is>
+          <t>TIGER TOUGH</t>
+        </is>
+      </c>
+      <c r="F345" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="G345" s="7" t="inlineStr">
+        <is>
+          <t>FULL REAR</t>
+        </is>
+      </c>
+      <c r="H345" s="7" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="I345" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J345" s="7" t="inlineStr"/>
+      <c r="K345" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="15" customHeight="1">
+      <c r="A346" s="9" t="n"/>
+      <c r="B346" s="10" t="inlineStr">
+        <is>
+          <t>Seat Covers</t>
+        </is>
+      </c>
+      <c r="C346" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E346" s="9" t="inlineStr">
+        <is>
+          <t>TIGER TOUGH</t>
+        </is>
+      </c>
+      <c r="F346" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="G346" s="9" t="inlineStr">
+        <is>
+          <t>FRONT AND REAR</t>
+        </is>
+      </c>
+      <c r="H346" s="9" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="I346" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J346" s="9" t="inlineStr"/>
+      <c r="K346" s="9" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="15" customHeight="1">
+      <c r="A347" s="7" t="n"/>
+      <c r="B347" s="8" t="inlineStr">
+        <is>
+          <t>Seat Covers</t>
+        </is>
+      </c>
+      <c r="C347" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D347" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E347" s="7" t="inlineStr">
+        <is>
+          <t>TIGER TOUGH</t>
+        </is>
+      </c>
+      <c r="F347" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="G347" s="7" t="inlineStr">
+        <is>
+          <t>SPECIFY MODEL</t>
+        </is>
+      </c>
+      <c r="H347" s="7" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="I347" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J347" s="7" t="inlineStr"/>
+      <c r="K347" s="7" t="inlineStr">
+        <is>
+          <t>loc sweep</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A176:K176"/>
+    <mergeCell ref="A258:K258"/>
+    <mergeCell ref="A314:K314"/>
     <mergeCell ref="H13:K13"/>
-    <mergeCell ref="A319:K319"/>
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A157:K157"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="H12:K12"/>
-    <mergeCell ref="A334:K334"/>
+    <mergeCell ref="A328:K328"/>
+    <mergeCell ref="A337:K337"/>
+    <mergeCell ref="A222:K222"/>
+    <mergeCell ref="A300:K300"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A110:K110"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="A325:K325"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A168:K168"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="H8:K8"/>
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A183:K183"/>
     <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A255:K255"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="H10:K10"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A238:K238"/>
     <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A154:K154"/>
-    <mergeCell ref="A210:K210"/>
+    <mergeCell ref="A272:K272"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A248:K248"/>
-    <mergeCell ref="A297:K297"/>
+    <mergeCell ref="A179:K179"/>
+    <mergeCell ref="A251:K251"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A235:K235"/>
-    <mergeCell ref="A269:K269"/>
+    <mergeCell ref="A213:K213"/>
+    <mergeCell ref="A322:K322"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A219:K219"/>
     <mergeCell ref="A106:K106"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A311:K311"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A206:K206"/>
-    <mergeCell ref="A180:K180"/>
+    <mergeCell ref="A171:K171"/>
+    <mergeCell ref="A209:K209"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C12:F12"/>
